--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -62932,6 +62932,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.96000003814697</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -62796,7 +62796,7 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
         <v>0</v>
@@ -62819,7 +62819,7 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
         <v>0</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>0</v>
@@ -62865,7 +62865,7 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
         <v>0</v>
@@ -62888,7 +62888,7 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
         <v>0</v>
@@ -62911,7 +62911,7 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
         <v>0</v>
@@ -62934,7 +62934,7 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
         <v>0</v>
@@ -62957,22 +62957,22 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="C2722" t="n">
-        <v>3.90000009536743</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>3.90000009536743</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="E2722" t="n">
-        <v>3.90000009536743</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="F2722" t="n">
-        <v>3.90000009536743</v>
+        <v>3.96000003814697</v>
       </c>
       <c r="G2722" t="s">
         <v>7</v>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63047,6 +63047,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2726" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63070,6 +63070,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63093,6 +63093,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2728" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63116,6 +63116,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63139,6 +63139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63162,6 +63162,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2731">
+      <c r="A2731" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2731" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2731" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63185,6 +63185,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63208,6 +63208,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2733">
+      <c r="A2733" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2733" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2733" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2733" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63231,6 +63231,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2734" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63254,6 +63254,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63277,6 +63277,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63300,6 +63300,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2737" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63323,6 +63323,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63392,6 +63392,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2741">
+      <c r="A2741" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2741" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2741" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2741" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2741" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2741" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2741" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63415,6 +63415,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2742">
+      <c r="A2742" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2742" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2742" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2742" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2742" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2742" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2742" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -63438,6 +63438,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2743" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G55" t="n">
-        <v>584.667785644531</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H55" t="n">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G56" t="n">
-        <v>584.667785644531</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G57" t="n">
-        <v>560.094787597656</v>
+        <v>560.0947265625</v>
       </c>
       <c r="H57" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G58" t="n">
-        <v>560.094787597656</v>
+        <v>560.0947265625</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G59" t="n">
-        <v>553.316101074219</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H59" t="n">
         <v>12</v>
@@ -2109,7 +2109,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G60" t="n">
-        <v>553.316101074219</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G61" t="n">
-        <v>553.316101074219</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>626.292724609375</v>
       </c>
       <c r="G62" t="n">
-        <v>556.705383300781</v>
+        <v>556.705444335938</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
@@ -2196,7 +2196,7 @@
         <v>664.899841308594</v>
       </c>
       <c r="G63" t="n">
-        <v>591.022827148438</v>
+        <v>591.022888183594</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -2631,7 +2631,7 @@
         <v>678.722106933594</v>
       </c>
       <c r="G78" t="n">
-        <v>603.309387207031</v>
+        <v>603.309326171875</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137878417969</v>
+        <v>618.137817382812</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137878417969</v>
+        <v>618.137817382812</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137878417969</v>
+        <v>618.137817382812</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137878417969</v>
+        <v>618.137817382812</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G100" t="n">
-        <v>584.667785644531</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H100" t="n">
         <v>9</v>
@@ -3298,7 +3298,7 @@
         <v>690.161254882812</v>
       </c>
       <c r="G101" t="n">
-        <v>613.477600097656</v>
+        <v>613.4775390625</v>
       </c>
       <c r="H101" t="n">
         <v>40</v>
@@ -3356,7 +3356,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G103" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H103" t="n">
         <v>4</v>
@@ -3385,7 +3385,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G104" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G105" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G106" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G107" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G108" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>671.096008300781</v>
       </c>
       <c r="G111" t="n">
-        <v>596.530639648438</v>
+        <v>596.530578613281</v>
       </c>
       <c r="H111" t="n">
         <v>3</v>
@@ -3617,7 +3617,7 @@
         <v>671.096008300781</v>
       </c>
       <c r="G112" t="n">
-        <v>596.530639648438</v>
+        <v>596.530578613281</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>671.096008300781</v>
       </c>
       <c r="G113" t="n">
-        <v>596.530639648438</v>
+        <v>596.530578613281</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G114" t="n">
-        <v>596.954223632812</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G115" t="n">
-        <v>596.954223632812</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G116" t="n">
-        <v>596.954223632812</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>672.04931640625</v>
       </c>
       <c r="G120" t="n">
-        <v>597.377990722656</v>
+        <v>597.3779296875</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
@@ -3936,7 +3936,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G123" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G124" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G125" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G126" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G140" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H140" t="n">
         <v>3</v>
@@ -4458,7 +4458,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G141" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G142" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G189" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H189" t="n">
         <v>22</v>
@@ -5879,7 +5879,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G190" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G191" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G192" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G193" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G194" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G195" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G196" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G197" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G198" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H198" t="n">
         <v>7</v>
@@ -6140,7 +6140,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G199" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G200" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G201" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G202" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G203" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G204" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G216" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H216" t="n">
         <v>18</v>
@@ -6662,7 +6662,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G217" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G218" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G219" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G220" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G226" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
@@ -6952,7 +6952,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G227" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G228" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G229" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G230" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G231" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G232" t="n">
-        <v>538.384887695312</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G240" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H240" t="n">
         <v>7</v>
@@ -7358,7 +7358,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G241" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G242" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G243" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G244" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G245" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H245" t="n">
         <v>193</v>
@@ -7503,7 +7503,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G246" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G247" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G248" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G249" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G250" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G251" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G252" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G253" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G254" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G255" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G256" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G257" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G258" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G259" t="n">
-        <v>553.389038085938</v>
+        <v>553.388977050781</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G260" t="n">
-        <v>553.389038085938</v>
+        <v>553.388977050781</v>
       </c>
       <c r="H260" t="n">
         <v>6</v>
@@ -8025,7 +8025,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G264" t="n">
-        <v>571.040954589844</v>
+        <v>571.040893554688</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -8054,7 +8054,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G265" t="n">
-        <v>571.040954589844</v>
+        <v>571.040893554688</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>627.246032714844</v>
       </c>
       <c r="G266" t="n">
-        <v>580.749572753906</v>
+        <v>580.74951171875</v>
       </c>
       <c r="H266" t="n">
         <v>3</v>
@@ -8112,7 +8112,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G267" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H267" t="n">
         <v>7</v>
@@ -8141,7 +8141,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G268" t="n">
-        <v>556.036804199219</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>601.984558105469</v>
       </c>
       <c r="G274" t="n">
-        <v>557.360656738281</v>
+        <v>557.360717773438</v>
       </c>
       <c r="H274" t="n">
         <v>7</v>
@@ -8344,7 +8344,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G275" t="n">
-        <v>557.802001953125</v>
+        <v>557.801940917969</v>
       </c>
       <c r="H275" t="n">
         <v>1</v>
@@ -8373,7 +8373,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G276" t="n">
-        <v>557.802001953125</v>
+        <v>557.801940917969</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>591.975341796875</v>
       </c>
       <c r="G277" t="n">
-        <v>548.093444824219</v>
+        <v>548.093383789062</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
@@ -8431,7 +8431,7 @@
         <v>591.022094726562</v>
       </c>
       <c r="G278" t="n">
-        <v>547.210815429688</v>
+        <v>547.210876464844</v>
       </c>
       <c r="H278" t="n">
         <v>15</v>
@@ -8489,7 +8489,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G280" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H280" t="n">
         <v>9</v>
@@ -8518,7 +8518,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G281" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G282" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G283" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>634.8720703125</v>
       </c>
       <c r="G297" t="n">
-        <v>587.810363769531</v>
+        <v>587.810302734375</v>
       </c>
       <c r="H297" t="n">
         <v>26</v>
@@ -9127,7 +9127,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G302" t="n">
-        <v>617.818664550781</v>
+        <v>617.818603515625</v>
       </c>
       <c r="H302" t="n">
         <v>28</v>
@@ -9185,7 +9185,7 @@
         <v>655.3671875</v>
       </c>
       <c r="G304" t="n">
-        <v>606.7861328125</v>
+        <v>606.786193847656</v>
       </c>
       <c r="H304" t="n">
         <v>34</v>
@@ -9214,7 +9214,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G305" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H305" t="n">
         <v>6</v>
@@ -9243,7 +9243,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G306" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G307" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G308" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G309" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>704.460205078125</v>
       </c>
       <c r="G311" t="n">
-        <v>652.240051269531</v>
+        <v>652.239990234375</v>
       </c>
       <c r="H311" t="n">
         <v>11</v>
@@ -9417,7 +9417,7 @@
         <v>704.460205078125</v>
       </c>
       <c r="G312" t="n">
-        <v>652.240051269531</v>
+        <v>652.239990234375</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G314" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H314" t="n">
         <v>39</v>
@@ -9504,7 +9504,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G315" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G316" t="n">
-        <v>636.794494628906</v>
+        <v>636.794555664062</v>
       </c>
       <c r="H316" t="n">
         <v>4</v>
@@ -9562,7 +9562,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G317" t="n">
-        <v>636.794494628906</v>
+        <v>636.794555664062</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G318" t="n">
-        <v>643.855285644531</v>
+        <v>643.855224609375</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -9649,7 +9649,7 @@
         <v>705.413452148438</v>
       </c>
       <c r="G320" t="n">
-        <v>653.12255859375</v>
+        <v>653.122619628906</v>
       </c>
       <c r="H320" t="n">
         <v>31</v>
@@ -9707,7 +9707,7 @@
         <v>714.946044921875</v>
       </c>
       <c r="G322" t="n">
-        <v>661.948608398438</v>
+        <v>661.948547363281</v>
       </c>
       <c r="H322" t="n">
         <v>9</v>
@@ -9765,7 +9765,7 @@
         <v>738.777587890625</v>
       </c>
       <c r="G324" t="n">
-        <v>684.013610839844</v>
+        <v>684.013549804688</v>
       </c>
       <c r="H324" t="n">
         <v>113</v>
@@ -9794,7 +9794,7 @@
         <v>756.889587402344</v>
       </c>
       <c r="G325" t="n">
-        <v>700.782958984375</v>
+        <v>700.782897949219</v>
       </c>
       <c r="H325" t="n">
         <v>4</v>
@@ -9881,7 +9881,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G328" t="n">
-        <v>741.38232421875</v>
+        <v>741.382385253906</v>
       </c>
       <c r="H328" t="n">
         <v>34</v>
@@ -9910,7 +9910,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G329" t="n">
-        <v>741.38232421875</v>
+        <v>741.382385253906</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>781.674377441406</v>
       </c>
       <c r="G330" t="n">
-        <v>723.73046875</v>
+        <v>723.730407714844</v>
       </c>
       <c r="H330" t="n">
         <v>3</v>
@@ -10200,7 +10200,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G339" t="n">
-        <v>732.556457519531</v>
+        <v>732.556396484375</v>
       </c>
       <c r="H339" t="n">
         <v>15</v>
@@ -10229,7 +10229,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G340" t="n">
-        <v>732.556457519531</v>
+        <v>732.556396484375</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>799.786315917969</v>
       </c>
       <c r="G341" t="n">
-        <v>740.499755859375</v>
+        <v>740.499816894531</v>
       </c>
       <c r="H341" t="n">
         <v>6</v>
@@ -10345,7 +10345,7 @@
         <v>822.664611816406</v>
       </c>
       <c r="G344" t="n">
-        <v>761.68212890625</v>
+        <v>761.682189941406</v>
       </c>
       <c r="H344" t="n">
         <v>18</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10432,7 +10432,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G347" t="n">
-        <v>776.686340332031</v>
+        <v>776.686401367188</v>
       </c>
       <c r="H347" t="n">
         <v>15</v>
@@ -10548,7 +10548,7 @@
         <v>855.075500488281</v>
       </c>
       <c r="G351" t="n">
-        <v>791.690490722656</v>
+        <v>791.690551757812</v>
       </c>
       <c r="H351" t="n">
         <v>349</v>
@@ -10693,7 +10693,7 @@
         <v>848.402648925781</v>
       </c>
       <c r="G356" t="n">
-        <v>785.512329101562</v>
+        <v>785.512268066406</v>
       </c>
       <c r="H356" t="n">
         <v>14</v>
@@ -10809,7 +10809,7 @@
         <v>867.467895507812</v>
       </c>
       <c r="G360" t="n">
-        <v>803.164245605469</v>
+        <v>803.164306640625</v>
       </c>
       <c r="H360" t="n">
         <v>47</v>
@@ -10983,7 +10983,7 @@
         <v>859.841796875</v>
       </c>
       <c r="G366" t="n">
-        <v>796.103515625</v>
+        <v>796.103454589844</v>
       </c>
       <c r="H366" t="n">
         <v>86</v>
@@ -11041,7 +11041,7 @@
         <v>850.309204101562</v>
       </c>
       <c r="G368" t="n">
-        <v>787.277526855469</v>
+        <v>787.277587890625</v>
       </c>
       <c r="H368" t="n">
         <v>15</v>
@@ -11070,7 +11070,7 @@
         <v>855.552124023438</v>
       </c>
       <c r="G369" t="n">
-        <v>792.131774902344</v>
+        <v>792.1318359375</v>
       </c>
       <c r="H369" t="n">
         <v>51</v>
@@ -11099,7 +11099,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G370" t="n">
-        <v>776.686340332031</v>
+        <v>776.686401367188</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>846.972778320312</v>
       </c>
       <c r="G371" t="n">
-        <v>784.188415527344</v>
+        <v>784.1884765625</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
@@ -11244,7 +11244,7 @@
         <v>856.50537109375</v>
       </c>
       <c r="G375" t="n">
-        <v>793.014404296875</v>
+        <v>793.014343261719</v>
       </c>
       <c r="H375" t="n">
         <v>17</v>
@@ -11360,7 +11360,7 @@
         <v>824.094482421875</v>
       </c>
       <c r="G379" t="n">
-        <v>763.006042480469</v>
+        <v>763.005981445312</v>
       </c>
       <c r="H379" t="n">
         <v>259</v>
@@ -11389,7 +11389,7 @@
         <v>827.907531738281</v>
       </c>
       <c r="G380" t="n">
-        <v>766.536499023438</v>
+        <v>766.536437988281</v>
       </c>
       <c r="H380" t="n">
         <v>36</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -79951,6 +79951,35 @@
         <v>0</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -746,7 +746,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G13" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G14" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G15" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G16" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G17" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G18" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G19" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G20" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G21" t="n">
-        <v>599.919921875</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>645.357971191406</v>
       </c>
       <c r="G27" t="n">
-        <v>573.652404785156</v>
+        <v>573.65234375</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -1529,7 +1529,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G40" t="n">
-        <v>555.0107421875</v>
+        <v>555.010803222656</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297302246094</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G57" t="n">
-        <v>560.094787597656</v>
+        <v>560.094848632812</v>
       </c>
       <c r="H57" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G58" t="n">
-        <v>560.094787597656</v>
+        <v>560.094848632812</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G64" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H64" t="n">
         <v>11</v>
@@ -2254,7 +2254,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G65" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G66" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G67" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G68" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G69" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G70" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G71" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G72" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G73" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G74" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G75" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G76" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G77" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G96" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
@@ -3182,7 +3182,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G97" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G98" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G99" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>664.423217773438</v>
       </c>
       <c r="G102" t="n">
-        <v>590.599182128906</v>
+        <v>590.599243164062</v>
       </c>
       <c r="H102" t="n">
         <v>53</v>
@@ -3356,7 +3356,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G103" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H103" t="n">
         <v>4</v>
@@ -3385,7 +3385,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G104" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G105" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G106" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G107" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G108" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G123" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G124" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G125" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G126" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G127" t="n">
-        <v>576.1943359375</v>
+        <v>576.194396972656</v>
       </c>
       <c r="H127" t="n">
         <v>1</v>
@@ -4081,7 +4081,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G128" t="n">
-        <v>576.1943359375</v>
+        <v>576.194396972656</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G129" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
@@ -80009,6 +80009,35 @@
         <v>0</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -1210,7 +1210,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G29" t="n">
-        <v>551.621337890625</v>
+        <v>551.621398925781</v>
       </c>
       <c r="H29" t="n">
         <v>20</v>
@@ -1239,7 +1239,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G30" t="n">
-        <v>551.621337890625</v>
+        <v>551.621398925781</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G31" t="n">
-        <v>551.621337890625</v>
+        <v>551.621398925781</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G32" t="n">
-        <v>551.621337890625</v>
+        <v>551.621398925781</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G40" t="n">
-        <v>555.010803222656</v>
+        <v>555.0107421875</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
@@ -1964,7 +1964,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G55" t="n">
-        <v>584.667846679688</v>
+        <v>584.667785644531</v>
       </c>
       <c r="H55" t="n">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G56" t="n">
-        <v>584.667846679688</v>
+        <v>584.667785644531</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G57" t="n">
-        <v>560.094848632812</v>
+        <v>560.094787597656</v>
       </c>
       <c r="H57" t="n">
         <v>12</v>
@@ -2051,7 +2051,7 @@
         <v>630.105773925781</v>
       </c>
       <c r="G58" t="n">
-        <v>560.094848632812</v>
+        <v>560.094787597656</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G59" t="n">
-        <v>553.316040039062</v>
+        <v>553.315979003906</v>
       </c>
       <c r="H59" t="n">
         <v>12</v>
@@ -2109,7 +2109,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G60" t="n">
-        <v>553.316040039062</v>
+        <v>553.315979003906</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G61" t="n">
-        <v>553.316040039062</v>
+        <v>553.315979003906</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>664.899841308594</v>
       </c>
       <c r="G63" t="n">
-        <v>591.02294921875</v>
+        <v>591.022888183594</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -2225,7 +2225,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G64" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H64" t="n">
         <v>11</v>
@@ -2254,7 +2254,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G65" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G66" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G67" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G68" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G69" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G70" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G71" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G72" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G73" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G74" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G75" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G76" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G77" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>678.722106933594</v>
       </c>
       <c r="G78" t="n">
-        <v>603.309448242188</v>
+        <v>603.309387207031</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G96" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
@@ -3182,7 +3182,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G97" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G98" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G99" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G100" t="n">
-        <v>584.667846679688</v>
+        <v>584.667785644531</v>
       </c>
       <c r="H100" t="n">
         <v>9</v>
@@ -3327,7 +3327,7 @@
         <v>664.423217773438</v>
       </c>
       <c r="G102" t="n">
-        <v>590.599243164062</v>
+        <v>590.599182128906</v>
       </c>
       <c r="H102" t="n">
         <v>53</v>
@@ -3356,7 +3356,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G103" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H103" t="n">
         <v>4</v>
@@ -3385,7 +3385,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G104" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G105" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G106" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G107" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G108" t="n">
-        <v>588.904479980469</v>
+        <v>588.904541015625</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G117" t="n">
-        <v>596.10693359375</v>
+        <v>596.106872558594</v>
       </c>
       <c r="H117" t="n">
         <v>3</v>
@@ -3791,7 +3791,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G118" t="n">
-        <v>596.10693359375</v>
+        <v>596.106872558594</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G119" t="n">
-        <v>596.10693359375</v>
+        <v>596.106872558594</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G123" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G124" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G125" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G126" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G127" t="n">
-        <v>576.194396972656</v>
+        <v>576.1943359375</v>
       </c>
       <c r="H127" t="n">
         <v>1</v>
@@ -4081,7 +4081,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G128" t="n">
-        <v>576.194396972656</v>
+        <v>576.1943359375</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G129" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
@@ -4139,7 +4139,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G130" t="n">
-        <v>604.579711914062</v>
+        <v>604.579650878906</v>
       </c>
       <c r="H130" t="n">
         <v>4</v>
@@ -4168,7 +4168,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G131" t="n">
-        <v>604.579711914062</v>
+        <v>604.579650878906</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G139" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H139" t="n">
         <v>1</v>
@@ -4777,7 +4777,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G152" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G153" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G154" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G155" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G156" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G157" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G158" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G159" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G160" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G161" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G162" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H162" t="n">
         <v>12</v>
@@ -5096,7 +5096,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G163" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G164" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G165" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G166" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G167" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G168" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G169" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G170" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G171" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G172" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G173" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G174" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G175" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G176" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G177" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G178" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G179" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G180" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G181" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G182" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G183" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G184" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G185" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G186" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G187" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G188" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G189" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H189" t="n">
         <v>22</v>
@@ -5879,7 +5879,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G190" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G191" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G192" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G193" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G194" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G195" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G196" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G197" t="n">
-        <v>573.688842773438</v>
+        <v>573.688781738281</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G198" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H198" t="n">
         <v>7</v>
@@ -6140,7 +6140,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G199" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G200" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G201" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G202" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G203" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G204" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G221" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H221" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G222" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G223" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G224" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G225" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.563110351562</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G261" t="n">
-        <v>570.158447265625</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H261" t="n">
         <v>7</v>
@@ -7967,7 +7967,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G262" t="n">
-        <v>570.158447265625</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G263" t="n">
-        <v>570.158447265625</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>627.246032714844</v>
       </c>
       <c r="G266" t="n">
-        <v>580.74951171875</v>
+        <v>580.749633789062</v>
       </c>
       <c r="H266" t="n">
         <v>3</v>
@@ -8170,7 +8170,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G269" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H269" t="n">
         <v>1</v>
@@ -8199,7 +8199,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G270" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G271" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G272" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G273" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>601.984558105469</v>
       </c>
       <c r="G274" t="n">
-        <v>557.360717773438</v>
+        <v>557.360656738281</v>
       </c>
       <c r="H274" t="n">
         <v>7</v>
@@ -8344,7 +8344,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G275" t="n">
-        <v>557.801940917969</v>
+        <v>557.802001953125</v>
       </c>
       <c r="H275" t="n">
         <v>1</v>
@@ -8373,7 +8373,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G276" t="n">
-        <v>557.801940917969</v>
+        <v>557.802001953125</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>591.975341796875</v>
       </c>
       <c r="G277" t="n">
-        <v>548.093383789062</v>
+        <v>548.093444824219</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
@@ -8431,7 +8431,7 @@
         <v>591.022094726562</v>
       </c>
       <c r="G278" t="n">
-        <v>547.210876464844</v>
+        <v>547.210815429688</v>
       </c>
       <c r="H278" t="n">
         <v>15</v>
@@ -8460,7 +8460,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G279" t="n">
-        <v>576.336547851562</v>
+        <v>576.336608886719</v>
       </c>
       <c r="H279" t="n">
         <v>11</v>
@@ -8489,7 +8489,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G280" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H280" t="n">
         <v>9</v>
@@ -8518,7 +8518,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G281" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G282" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G283" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G290" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H290" t="n">
         <v>94</v>
@@ -8808,7 +8808,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G291" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>650.124267578125</v>
       </c>
       <c r="G292" t="n">
-        <v>601.931823730469</v>
+        <v>601.931884765625</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -8866,7 +8866,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G293" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H293" t="n">
         <v>7</v>
@@ -8895,7 +8895,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G294" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G295" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G296" t="n">
-        <v>591.340637207031</v>
+        <v>591.340698242188</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>634.8720703125</v>
       </c>
       <c r="G297" t="n">
-        <v>587.810302734375</v>
+        <v>587.810363769531</v>
       </c>
       <c r="H297" t="n">
         <v>26</v>
@@ -9011,7 +9011,7 @@
         <v>645.834594726562</v>
       </c>
       <c r="G298" t="n">
-        <v>597.960205078125</v>
+        <v>597.960144042969</v>
       </c>
       <c r="H298" t="n">
         <v>3</v>
@@ -9040,7 +9040,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G299" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H299" t="n">
         <v>4</v>
@@ -9069,7 +9069,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G300" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>658.70361328125</v>
       </c>
       <c r="G303" t="n">
-        <v>609.875244140625</v>
+        <v>609.875305175781</v>
       </c>
       <c r="H303" t="n">
         <v>3</v>
@@ -9185,7 +9185,7 @@
         <v>655.3671875</v>
       </c>
       <c r="G304" t="n">
-        <v>606.786193847656</v>
+        <v>606.7861328125</v>
       </c>
       <c r="H304" t="n">
         <v>34</v>
@@ -9214,7 +9214,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G305" t="n">
-        <v>623.1142578125</v>
+        <v>623.114196777344</v>
       </c>
       <c r="H305" t="n">
         <v>6</v>
@@ -9243,7 +9243,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G306" t="n">
-        <v>623.1142578125</v>
+        <v>623.114196777344</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G307" t="n">
-        <v>623.1142578125</v>
+        <v>623.114196777344</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G308" t="n">
-        <v>623.1142578125</v>
+        <v>623.114196777344</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G309" t="n">
-        <v>623.1142578125</v>
+        <v>623.114196777344</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G314" t="n">
-        <v>636.353149414062</v>
+        <v>636.353210449219</v>
       </c>
       <c r="H314" t="n">
         <v>39</v>
@@ -9504,7 +9504,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G315" t="n">
-        <v>636.353149414062</v>
+        <v>636.353210449219</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G318" t="n">
-        <v>643.855285644531</v>
+        <v>643.855224609375</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -9707,7 +9707,7 @@
         <v>714.946044921875</v>
       </c>
       <c r="G322" t="n">
-        <v>661.948547363281</v>
+        <v>661.948608398438</v>
       </c>
       <c r="H322" t="n">
         <v>9</v>
@@ -9794,7 +9794,7 @@
         <v>756.889587402344</v>
       </c>
       <c r="G325" t="n">
-        <v>700.782897949219</v>
+        <v>700.782958984375</v>
       </c>
       <c r="H325" t="n">
         <v>4</v>
@@ -9939,7 +9939,7 @@
         <v>781.674377441406</v>
       </c>
       <c r="G330" t="n">
-        <v>723.730407714844</v>
+        <v>723.73046875</v>
       </c>
       <c r="H330" t="n">
         <v>3</v>
@@ -9997,7 +9997,7 @@
         <v>787.393920898438</v>
       </c>
       <c r="G332" t="n">
-        <v>729.026123046875</v>
+        <v>729.026000976562</v>
       </c>
       <c r="H332" t="n">
         <v>22</v>
@@ -10026,7 +10026,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G333" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H333" t="n">
         <v>25</v>
@@ -10055,7 +10055,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G334" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G335" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>790.253723144531</v>
       </c>
       <c r="G338" t="n">
-        <v>731.673889160156</v>
+        <v>731.673828125</v>
       </c>
       <c r="H338" t="n">
         <v>22</v>
@@ -10287,7 +10287,7 @@
         <v>805.505920410156</v>
       </c>
       <c r="G342" t="n">
-        <v>745.795349121094</v>
+        <v>745.79541015625</v>
       </c>
       <c r="H342" t="n">
         <v>25</v>
@@ -10316,7 +10316,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G343" t="n">
-        <v>758.593017578125</v>
+        <v>758.593078613281</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -10345,7 +10345,7 @@
         <v>822.664611816406</v>
       </c>
       <c r="G344" t="n">
-        <v>761.682189941406</v>
+        <v>761.68212890625</v>
       </c>
       <c r="H344" t="n">
         <v>18</v>
@@ -10374,7 +10374,7 @@
         <v>819.804809570312</v>
       </c>
       <c r="G345" t="n">
-        <v>759.034362792969</v>
+        <v>759.034301757812</v>
       </c>
       <c r="H345" t="n">
         <v>20</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.860412597656</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10432,7 +10432,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G347" t="n">
-        <v>776.686401367188</v>
+        <v>776.686340332031</v>
       </c>
       <c r="H347" t="n">
         <v>15</v>
@@ -10519,7 +10519,7 @@
         <v>924.66357421875</v>
       </c>
       <c r="G350" t="n">
-        <v>856.120178222656</v>
+        <v>856.1201171875</v>
       </c>
       <c r="H350" t="n">
         <v>99</v>
@@ -10548,7 +10548,7 @@
         <v>855.075500488281</v>
       </c>
       <c r="G351" t="n">
-        <v>791.690490722656</v>
+        <v>791.6904296875</v>
       </c>
       <c r="H351" t="n">
         <v>349</v>
@@ -10577,7 +10577,7 @@
         <v>833.150451660156</v>
       </c>
       <c r="G352" t="n">
-        <v>771.390686035156</v>
+        <v>771.390747070312</v>
       </c>
       <c r="H352" t="n">
         <v>240</v>
@@ -10606,7 +10606,7 @@
         <v>826.477661132812</v>
       </c>
       <c r="G353" t="n">
-        <v>765.212524414062</v>
+        <v>765.212585449219</v>
       </c>
       <c r="H353" t="n">
         <v>69</v>
@@ -10635,7 +10635,7 @@
         <v>837.916748046875</v>
       </c>
       <c r="G354" t="n">
-        <v>775.803649902344</v>
+        <v>775.8037109375</v>
       </c>
       <c r="H354" t="n">
         <v>25</v>
@@ -10722,7 +10722,7 @@
         <v>852.692321777344</v>
       </c>
       <c r="G357" t="n">
-        <v>789.484069824219</v>
+        <v>789.484008789062</v>
       </c>
       <c r="H357" t="n">
         <v>37</v>
@@ -10751,7 +10751,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G358" t="n">
-        <v>789.042724609375</v>
+        <v>789.042663574219</v>
       </c>
       <c r="H358" t="n">
         <v>14</v>
@@ -10809,7 +10809,7 @@
         <v>867.467895507812</v>
       </c>
       <c r="G360" t="n">
-        <v>803.164306640625</v>
+        <v>803.164245605469</v>
       </c>
       <c r="H360" t="n">
         <v>47</v>
@@ -10896,7 +10896,7 @@
         <v>844.112976074219</v>
       </c>
       <c r="G363" t="n">
-        <v>781.540588378906</v>
+        <v>781.540649414062</v>
       </c>
       <c r="H363" t="n">
         <v>11</v>
@@ -10983,7 +10983,7 @@
         <v>859.841796875</v>
       </c>
       <c r="G366" t="n">
-        <v>796.103515625</v>
+        <v>796.103454589844</v>
       </c>
       <c r="H366" t="n">
         <v>86</v>
@@ -11012,7 +11012,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G367" t="n">
-        <v>789.042724609375</v>
+        <v>789.042663574219</v>
       </c>
       <c r="H367" t="n">
         <v>81</v>
@@ -11070,7 +11070,7 @@
         <v>855.552124023438</v>
       </c>
       <c r="G369" t="n">
-        <v>792.131774902344</v>
+        <v>792.1318359375</v>
       </c>
       <c r="H369" t="n">
         <v>51</v>
@@ -11099,7 +11099,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G370" t="n">
-        <v>776.686401367188</v>
+        <v>776.686340332031</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11157,7 +11157,7 @@
         <v>844.112976074219</v>
       </c>
       <c r="G372" t="n">
-        <v>781.540588378906</v>
+        <v>781.540649414062</v>
       </c>
       <c r="H372" t="n">
         <v>22</v>
@@ -11186,7 +11186,7 @@
         <v>847.449401855469</v>
       </c>
       <c r="G373" t="n">
-        <v>784.629638671875</v>
+        <v>784.629699707031</v>
       </c>
       <c r="H373" t="n">
         <v>28</v>
@@ -11302,7 +11302,7 @@
         <v>846.019470214844</v>
       </c>
       <c r="G377" t="n">
-        <v>783.305847167969</v>
+        <v>783.305786132812</v>
       </c>
       <c r="H377" t="n">
         <v>94</v>
@@ -11360,7 +11360,7 @@
         <v>824.094482421875</v>
       </c>
       <c r="G379" t="n">
-        <v>763.005981445312</v>
+        <v>763.006042480469</v>
       </c>
       <c r="H379" t="n">
         <v>259</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.860412597656</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -11534,7 +11534,7 @@
         <v>822.18798828125</v>
       </c>
       <c r="G385" t="n">
-        <v>787.52978515625</v>
+        <v>787.529846191406</v>
       </c>
       <c r="H385" t="n">
         <v>11</v>
@@ -11563,7 +11563,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G386" t="n">
-        <v>784.79052734375</v>
+        <v>784.790588378906</v>
       </c>
       <c r="H386" t="n">
         <v>80</v>
@@ -11592,7 +11592,7 @@
         <v>795.973266601562</v>
       </c>
       <c r="G387" t="n">
-        <v>762.420166015625</v>
+        <v>762.420104980469</v>
       </c>
       <c r="H387" t="n">
         <v>140</v>
@@ -11679,7 +11679,7 @@
         <v>811.225463867188</v>
       </c>
       <c r="G390" t="n">
-        <v>777.029479980469</v>
+        <v>777.029418945312</v>
       </c>
       <c r="H390" t="n">
         <v>45</v>
@@ -11766,7 +11766,7 @@
         <v>814.085266113281</v>
       </c>
       <c r="G393" t="n">
-        <v>779.768676757812</v>
+        <v>779.768615722656</v>
       </c>
       <c r="H393" t="n">
         <v>14</v>
@@ -11882,7 +11882,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G397" t="n">
-        <v>803.508728027344</v>
+        <v>803.508666992188</v>
       </c>
       <c r="H397" t="n">
         <v>472</v>
@@ -11911,7 +11911,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G398" t="n">
-        <v>803.508728027344</v>
+        <v>803.508666992188</v>
       </c>
       <c r="H398" t="n">
         <v>1</v>
@@ -11998,7 +11998,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G401" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H401" t="n">
         <v>3</v>
@@ -12027,7 +12027,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G402" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G403" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G404" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G407" t="n">
-        <v>780.681762695312</v>
+        <v>780.681701660156</v>
       </c>
       <c r="H407" t="n">
         <v>176</v>
@@ -12259,7 +12259,7 @@
         <v>815.991760253906</v>
       </c>
       <c r="G410" t="n">
-        <v>781.594848632812</v>
+        <v>781.594787597656</v>
       </c>
       <c r="H410" t="n">
         <v>51</v>
@@ -12288,7 +12288,7 @@
         <v>812.655334472656</v>
       </c>
       <c r="G411" t="n">
-        <v>778.399047851562</v>
+        <v>778.398986816406</v>
       </c>
       <c r="H411" t="n">
         <v>72</v>
@@ -12375,7 +12375,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G414" t="n">
-        <v>776.116333007812</v>
+        <v>776.116271972656</v>
       </c>
       <c r="H414" t="n">
         <v>102</v>
@@ -12404,7 +12404,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G415" t="n">
-        <v>776.116333007812</v>
+        <v>776.116271972656</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G416" t="n">
-        <v>780.681762695312</v>
+        <v>780.681701660156</v>
       </c>
       <c r="H416" t="n">
         <v>110</v>
@@ -12549,7 +12549,7 @@
         <v>865.084716796875</v>
       </c>
       <c r="G420" t="n">
-        <v>828.618347167969</v>
+        <v>828.618286132812</v>
       </c>
       <c r="H420" t="n">
         <v>44</v>
@@ -12752,7 +12752,7 @@
         <v>895.112487792969</v>
       </c>
       <c r="G427" t="n">
-        <v>857.380310058594</v>
+        <v>857.38037109375</v>
       </c>
       <c r="H427" t="n">
         <v>253</v>
@@ -13100,7 +13100,7 @@
         <v>1046.68103027344</v>
       </c>
       <c r="G439" t="n">
-        <v>1002.55969238281</v>
+        <v>1002.55963134766</v>
       </c>
       <c r="H439" t="n">
         <v>95</v>
@@ -13216,7 +13216,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G443" t="n">
-        <v>1010.77734375</v>
+        <v>1010.77740478516</v>
       </c>
       <c r="H443" t="n">
         <v>187</v>
@@ -13245,7 +13245,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G444" t="n">
-        <v>1010.77734375</v>
+        <v>1010.77740478516</v>
       </c>
       <c r="H444" t="n">
         <v>22</v>
@@ -13506,7 +13506,7 @@
         <v>1009.50384521484</v>
       </c>
       <c r="G453" t="n">
-        <v>966.94970703125</v>
+        <v>966.949645996094</v>
       </c>
       <c r="H453" t="n">
         <v>51</v>
@@ -13564,7 +13564,7 @@
         <v>1043.8212890625</v>
       </c>
       <c r="G455" t="n">
-        <v>999.820495605469</v>
+        <v>999.820556640625</v>
       </c>
       <c r="H455" t="n">
         <v>188</v>
@@ -13593,7 +13593,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G456" t="n">
-        <v>1013.5166015625</v>
+        <v>1013.51666259766</v>
       </c>
       <c r="H456" t="n">
         <v>14</v>
@@ -13622,7 +13622,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G457" t="n">
-        <v>1022.6474609375</v>
+        <v>1022.64752197266</v>
       </c>
       <c r="H457" t="n">
         <v>23</v>
@@ -13651,7 +13651,7 @@
         <v>1061.93322753906</v>
       </c>
       <c r="G458" t="n">
-        <v>1017.1689453125</v>
+        <v>1017.16888427734</v>
       </c>
       <c r="H458" t="n">
         <v>240</v>
@@ -13767,7 +13767,7 @@
         <v>1021.89624023438</v>
       </c>
       <c r="G462" t="n">
-        <v>978.819702148438</v>
+        <v>978.819641113281</v>
       </c>
       <c r="H462" t="n">
         <v>56</v>
@@ -13854,7 +13854,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G465" t="n">
-        <v>1022.6474609375</v>
+        <v>1022.64752197266</v>
       </c>
       <c r="H465" t="n">
         <v>176</v>
@@ -13883,7 +13883,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G466" t="n">
-        <v>1031.77819824219</v>
+        <v>1031.77807617188</v>
       </c>
       <c r="H466" t="n">
         <v>15</v>
@@ -13912,7 +13912,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G467" t="n">
-        <v>1013.5166015625</v>
+        <v>1013.51666259766</v>
       </c>
       <c r="H467" t="n">
         <v>33</v>
@@ -14028,7 +14028,7 @@
         <v>1083.85827636719</v>
       </c>
       <c r="G471" t="n">
-        <v>1038.16979980469</v>
+        <v>1038.16967773438</v>
       </c>
       <c r="H471" t="n">
         <v>11</v>
@@ -14057,7 +14057,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G472" t="n">
-        <v>1031.77819824219</v>
+        <v>1031.77807617188</v>
       </c>
       <c r="H472" t="n">
         <v>23</v>
@@ -14086,7 +14086,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G473" t="n">
-        <v>1031.77819824219</v>
+        <v>1031.77807617188</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1074.32556152344</v>
       </c>
       <c r="G475" t="n">
-        <v>1029.03894042969</v>
+        <v>1029.03881835938</v>
       </c>
       <c r="H475" t="n">
         <v>40</v>
@@ -14289,7 +14289,7 @@
         <v>1003.78424072266</v>
       </c>
       <c r="G480" t="n">
-        <v>961.471130371094</v>
+        <v>961.47119140625</v>
       </c>
       <c r="H480" t="n">
         <v>14</v>
@@ -14318,7 +14318,7 @@
         <v>976.139709472656</v>
       </c>
       <c r="G481" t="n">
-        <v>934.991882324219</v>
+        <v>934.991943359375</v>
       </c>
       <c r="H481" t="n">
         <v>292</v>
@@ -14347,7 +14347,7 @@
         <v>976.139709472656</v>
       </c>
       <c r="G482" t="n">
-        <v>934.991882324219</v>
+        <v>934.991943359375</v>
       </c>
       <c r="H482" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G484" t="n">
-        <v>903.947265625</v>
+        <v>903.947326660156</v>
       </c>
       <c r="H484" t="n">
         <v>51</v>
@@ -14434,7 +14434,7 @@
         <v>975.186401367188</v>
       </c>
       <c r="G485" t="n">
-        <v>934.078796386719</v>
+        <v>934.078857421875</v>
       </c>
       <c r="H485" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>975.186401367188</v>
       </c>
       <c r="G486" t="n">
-        <v>934.078796386719</v>
+        <v>934.078857421875</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>950.878234863281</v>
       </c>
       <c r="G487" t="n">
-        <v>910.795349121094</v>
+        <v>910.795288085938</v>
       </c>
       <c r="H487" t="n">
         <v>12</v>
@@ -14608,7 +14608,7 @@
         <v>988.532104492188</v>
       </c>
       <c r="G491" t="n">
-        <v>946.861938476562</v>
+        <v>946.861999511719</v>
       </c>
       <c r="H491" t="n">
         <v>20</v>
@@ -14695,7 +14695,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G494" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H494" t="n">
         <v>6</v>
@@ -14724,7 +14724,7 @@
         <v>963.747253417969</v>
       </c>
       <c r="G495" t="n">
-        <v>923.121826171875</v>
+        <v>923.121887207031</v>
       </c>
       <c r="H495" t="n">
         <v>18</v>
@@ -14869,7 +14869,7 @@
         <v>976.139709472656</v>
       </c>
       <c r="G500" t="n">
-        <v>934.991882324219</v>
+        <v>934.991943359375</v>
       </c>
       <c r="H500" t="n">
         <v>40</v>
@@ -15594,7 +15594,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G525" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H525" t="n">
         <v>7</v>
@@ -16000,7 +16000,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G539" t="n">
-        <v>903.947265625</v>
+        <v>903.947326660156</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -16087,7 +16087,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G542" t="n">
-        <v>903.947265625</v>
+        <v>903.947326660156</v>
       </c>
       <c r="H542" t="n">
         <v>1</v>
@@ -16464,7 +16464,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G555" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H555" t="n">
         <v>214</v>
@@ -16493,7 +16493,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G556" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H556" t="n">
         <v>15</v>
@@ -16522,7 +16522,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G557" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H557" t="n">
         <v>15</v>
@@ -16580,7 +16580,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G559" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H559" t="n">
         <v>103</v>
@@ -16841,7 +16841,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G568" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H568" t="n">
         <v>4</v>
@@ -17015,7 +17015,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G574" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H574" t="n">
         <v>34</v>
@@ -17102,7 +17102,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G577" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H577" t="n">
         <v>89</v>
@@ -17131,7 +17131,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G578" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G583" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H583" t="n">
         <v>3</v>
@@ -17305,7 +17305,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G584" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H584" t="n">
         <v>129</v>
@@ -17740,7 +17740,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G599" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H599" t="n">
         <v>7</v>
@@ -17885,7 +17885,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G604" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H604" t="n">
         <v>3</v>
@@ -18146,7 +18146,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G613" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H613" t="n">
         <v>3</v>
@@ -18262,7 +18262,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G617" t="n">
-        <v>949.60107421875</v>
+        <v>949.601135253906</v>
       </c>
       <c r="H617" t="n">
         <v>3</v>
@@ -18349,7 +18349,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G620" t="n">
-        <v>903.947265625</v>
+        <v>903.947326660156</v>
       </c>
       <c r="H620" t="n">
         <v>6</v>
@@ -80038,6 +80038,35 @@
         <v>0</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G2" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G3" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -485,7 +485,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G4" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G5" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G6" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G7" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G8" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G9" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G22" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1036,7 +1036,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G23" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G24" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G25" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G26" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G28" t="n">
-        <v>567.720886230469</v>
+        <v>567.720947265625</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1326,7 +1326,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G33" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
@@ -1355,7 +1355,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G34" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G35" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G36" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G37" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G38" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G39" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G40" t="n">
-        <v>555.0107421875</v>
+        <v>555.010681152344</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
@@ -1558,7 +1558,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G41" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
@@ -1587,7 +1587,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G42" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G43" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H43" t="n">
         <v>7</v>
@@ -1645,7 +1645,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G44" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G45" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G46" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G47" t="n">
-        <v>566.026306152344</v>
+        <v>566.026245117188</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297241210938</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G59" t="n">
-        <v>553.315979003906</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H59" t="n">
         <v>12</v>
@@ -2109,7 +2109,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G60" t="n">
-        <v>553.315979003906</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G61" t="n">
-        <v>553.315979003906</v>
+        <v>553.316040039062</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>664.899841308594</v>
       </c>
       <c r="G63" t="n">
-        <v>591.022888183594</v>
+        <v>591.022827148438</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G83" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H83" t="n">
         <v>39</v>
@@ -2805,7 +2805,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G84" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G85" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G86" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G87" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G88" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G89" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G90" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G91" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G92" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G93" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G94" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G95" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>690.161254882812</v>
       </c>
       <c r="G101" t="n">
-        <v>613.4775390625</v>
+        <v>613.477600097656</v>
       </c>
       <c r="H101" t="n">
         <v>40</v>
@@ -3327,7 +3327,7 @@
         <v>664.423217773438</v>
       </c>
       <c r="G102" t="n">
-        <v>590.599182128906</v>
+        <v>590.599243164062</v>
       </c>
       <c r="H102" t="n">
         <v>53</v>
@@ -3530,7 +3530,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G109" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H109" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G110" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G114" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G115" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G116" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G117" t="n">
-        <v>596.106872558594</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H117" t="n">
         <v>3</v>
@@ -3791,7 +3791,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G118" t="n">
-        <v>596.106872558594</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G119" t="n">
-        <v>596.106872558594</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>672.04931640625</v>
       </c>
       <c r="G120" t="n">
-        <v>597.378051757812</v>
+        <v>597.377990722656</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
@@ -3878,7 +3878,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G121" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H121" t="n">
         <v>3</v>
@@ -3907,7 +3907,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G122" t="n">
-        <v>593.141235351562</v>
+        <v>593.141296386719</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G123" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G124" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G125" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G126" t="n">
-        <v>593.565002441406</v>
+        <v>593.56494140625</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G130" t="n">
-        <v>604.579650878906</v>
+        <v>604.579711914062</v>
       </c>
       <c r="H130" t="n">
         <v>4</v>
@@ -4168,7 +4168,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G131" t="n">
-        <v>604.579650878906</v>
+        <v>604.579711914062</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G139" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H139" t="n">
         <v>1</v>
@@ -4429,7 +4429,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G140" t="n">
-        <v>594.87109375</v>
+        <v>594.871154785156</v>
       </c>
       <c r="H140" t="n">
         <v>3</v>
@@ -4458,7 +4458,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G141" t="n">
-        <v>594.87109375</v>
+        <v>594.871154785156</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G142" t="n">
-        <v>594.87109375</v>
+        <v>594.871154785156</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G143" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H143" t="n">
         <v>1</v>
@@ -4545,7 +4545,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G144" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G145" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G146" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G147" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G148" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G149" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G150" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>643.451477050781</v>
       </c>
       <c r="G151" t="n">
-        <v>595.753784179688</v>
+        <v>595.753723144531</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G152" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G153" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G154" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G155" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G156" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G157" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G158" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G159" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G160" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G161" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G162" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H162" t="n">
         <v>12</v>
@@ -5096,7 +5096,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G163" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G164" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G165" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G166" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G167" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G168" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G169" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G170" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G171" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G172" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G173" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G174" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G175" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G176" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G177" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G178" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G179" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G180" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G181" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G182" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G183" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G184" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G185" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G186" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G187" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G188" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G198" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H198" t="n">
         <v>7</v>
@@ -6140,7 +6140,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G199" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G200" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G201" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G202" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G203" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G204" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G216" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H216" t="n">
         <v>18</v>
@@ -6662,7 +6662,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G217" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G218" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G219" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G220" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.563049316406</v>
+        <v>544.563110351562</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G240" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H240" t="n">
         <v>7</v>
@@ -7358,7 +7358,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G241" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G242" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G243" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G244" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G245" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H245" t="n">
         <v>193</v>
@@ -7503,7 +7503,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G246" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G247" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G248" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G249" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G250" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G251" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G252" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G253" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G254" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G255" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G256" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G257" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G258" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G259" t="n">
-        <v>553.388977050781</v>
+        <v>553.389038085938</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G260" t="n">
-        <v>553.388977050781</v>
+        <v>553.389038085938</v>
       </c>
       <c r="H260" t="n">
         <v>6</v>
@@ -7938,7 +7938,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G261" t="n">
-        <v>570.158386230469</v>
+        <v>570.158325195312</v>
       </c>
       <c r="H261" t="n">
         <v>7</v>
@@ -7967,7 +7967,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G262" t="n">
-        <v>570.158386230469</v>
+        <v>570.158325195312</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G263" t="n">
-        <v>570.158386230469</v>
+        <v>570.158325195312</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>627.246032714844</v>
       </c>
       <c r="G266" t="n">
-        <v>580.749633789062</v>
+        <v>580.749572753906</v>
       </c>
       <c r="H266" t="n">
         <v>3</v>
@@ -8112,7 +8112,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G267" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H267" t="n">
         <v>7</v>
@@ -8141,7 +8141,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G268" t="n">
-        <v>556.036804199219</v>
+        <v>556.036865234375</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G269" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H269" t="n">
         <v>1</v>
@@ -8199,7 +8199,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G270" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G271" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G272" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G273" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>601.984558105469</v>
       </c>
       <c r="G274" t="n">
-        <v>557.360656738281</v>
+        <v>557.360717773438</v>
       </c>
       <c r="H274" t="n">
         <v>7</v>
@@ -8460,7 +8460,7 @@
         <v>622.479675292969</v>
       </c>
       <c r="G279" t="n">
-        <v>576.336608886719</v>
+        <v>576.336547851562</v>
       </c>
       <c r="H279" t="n">
         <v>11</v>
@@ -8489,7 +8489,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G280" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H280" t="n">
         <v>9</v>
@@ -8518,7 +8518,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G281" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G282" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G283" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>645.834594726562</v>
       </c>
       <c r="G298" t="n">
-        <v>597.960144042969</v>
+        <v>597.960266113281</v>
       </c>
       <c r="H298" t="n">
         <v>3</v>
@@ -9040,7 +9040,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G299" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H299" t="n">
         <v>4</v>
@@ -9069,7 +9069,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G300" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G302" t="n">
-        <v>617.818664550781</v>
+        <v>617.818603515625</v>
       </c>
       <c r="H302" t="n">
         <v>28</v>
@@ -9156,7 +9156,7 @@
         <v>658.70361328125</v>
       </c>
       <c r="G303" t="n">
-        <v>609.875305175781</v>
+        <v>609.875244140625</v>
       </c>
       <c r="H303" t="n">
         <v>3</v>
@@ -9185,7 +9185,7 @@
         <v>655.3671875</v>
       </c>
       <c r="G304" t="n">
-        <v>606.7861328125</v>
+        <v>606.786193847656</v>
       </c>
       <c r="H304" t="n">
         <v>34</v>
@@ -9214,7 +9214,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G305" t="n">
-        <v>623.114196777344</v>
+        <v>623.1142578125</v>
       </c>
       <c r="H305" t="n">
         <v>6</v>
@@ -9243,7 +9243,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G306" t="n">
-        <v>623.114196777344</v>
+        <v>623.1142578125</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G307" t="n">
-        <v>623.114196777344</v>
+        <v>623.1142578125</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G308" t="n">
-        <v>623.114196777344</v>
+        <v>623.1142578125</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G309" t="n">
-        <v>623.114196777344</v>
+        <v>623.1142578125</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G310" t="n">
-        <v>626.644653320312</v>
+        <v>626.644714355469</v>
       </c>
       <c r="H310" t="n">
         <v>7</v>
@@ -9388,7 +9388,7 @@
         <v>704.460205078125</v>
       </c>
       <c r="G311" t="n">
-        <v>652.239990234375</v>
+        <v>652.240051269531</v>
       </c>
       <c r="H311" t="n">
         <v>11</v>
@@ -9417,7 +9417,7 @@
         <v>704.460205078125</v>
       </c>
       <c r="G312" t="n">
-        <v>652.239990234375</v>
+        <v>652.240051269531</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G313" t="n">
-        <v>626.644653320312</v>
+        <v>626.644714355469</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -9533,7 +9533,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G316" t="n">
-        <v>636.794494628906</v>
+        <v>636.794555664062</v>
       </c>
       <c r="H316" t="n">
         <v>4</v>
@@ -9562,7 +9562,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G317" t="n">
-        <v>636.794494628906</v>
+        <v>636.794555664062</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G318" t="n">
-        <v>643.855224609375</v>
+        <v>643.855285644531</v>
       </c>
       <c r="H318" t="n">
         <v>9</v>
@@ -9707,7 +9707,7 @@
         <v>714.946044921875</v>
       </c>
       <c r="G322" t="n">
-        <v>661.948608398438</v>
+        <v>661.948547363281</v>
       </c>
       <c r="H322" t="n">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>785.0107421875</v>
       </c>
       <c r="G327" t="n">
-        <v>726.819519042969</v>
+        <v>726.819458007812</v>
       </c>
       <c r="H327" t="n">
         <v>11</v>
@@ -9968,7 +9968,7 @@
         <v>787.870544433594</v>
       </c>
       <c r="G331" t="n">
-        <v>729.46728515625</v>
+        <v>729.467346191406</v>
       </c>
       <c r="H331" t="n">
         <v>6</v>
@@ -9997,7 +9997,7 @@
         <v>787.393920898438</v>
       </c>
       <c r="G332" t="n">
-        <v>729.026000976562</v>
+        <v>729.025939941406</v>
       </c>
       <c r="H332" t="n">
         <v>22</v>
@@ -10287,7 +10287,7 @@
         <v>805.505920410156</v>
       </c>
       <c r="G342" t="n">
-        <v>745.79541015625</v>
+        <v>745.795471191406</v>
       </c>
       <c r="H342" t="n">
         <v>25</v>
@@ -10316,7 +10316,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G343" t="n">
-        <v>758.593078613281</v>
+        <v>758.593017578125</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.8603515625</v>
+        <v>767.860290527344</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10432,7 +10432,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G347" t="n">
-        <v>776.686340332031</v>
+        <v>776.686401367188</v>
       </c>
       <c r="H347" t="n">
         <v>15</v>
@@ -10461,7 +10461,7 @@
         <v>912.747802734375</v>
       </c>
       <c r="G348" t="n">
-        <v>845.087768554688</v>
+        <v>845.087707519531</v>
       </c>
       <c r="H348" t="n">
         <v>69</v>
@@ -10490,7 +10490,7 @@
         <v>969.466857910156</v>
       </c>
       <c r="G349" t="n">
-        <v>897.602233886719</v>
+        <v>897.602294921875</v>
       </c>
       <c r="H349" t="n">
         <v>124</v>
@@ -10548,7 +10548,7 @@
         <v>855.075500488281</v>
       </c>
       <c r="G351" t="n">
-        <v>791.6904296875</v>
+        <v>791.690490722656</v>
       </c>
       <c r="H351" t="n">
         <v>349</v>
@@ -10577,7 +10577,7 @@
         <v>833.150451660156</v>
       </c>
       <c r="G352" t="n">
-        <v>771.390747070312</v>
+        <v>771.390686035156</v>
       </c>
       <c r="H352" t="n">
         <v>240</v>
@@ -10635,7 +10635,7 @@
         <v>837.916748046875</v>
       </c>
       <c r="G354" t="n">
-        <v>775.8037109375</v>
+        <v>775.803649902344</v>
       </c>
       <c r="H354" t="n">
         <v>25</v>
@@ -10664,7 +10664,7 @@
         <v>845.066223144531</v>
       </c>
       <c r="G355" t="n">
-        <v>782.423156738281</v>
+        <v>782.423217773438</v>
       </c>
       <c r="H355" t="n">
         <v>31</v>
@@ -10693,7 +10693,7 @@
         <v>848.402648925781</v>
       </c>
       <c r="G356" t="n">
-        <v>785.512268066406</v>
+        <v>785.512329101562</v>
       </c>
       <c r="H356" t="n">
         <v>14</v>
@@ -10751,7 +10751,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G358" t="n">
-        <v>789.042663574219</v>
+        <v>789.042724609375</v>
       </c>
       <c r="H358" t="n">
         <v>14</v>
@@ -10809,7 +10809,7 @@
         <v>867.467895507812</v>
       </c>
       <c r="G360" t="n">
-        <v>803.164245605469</v>
+        <v>803.164306640625</v>
       </c>
       <c r="H360" t="n">
         <v>47</v>
@@ -10896,7 +10896,7 @@
         <v>844.112976074219</v>
       </c>
       <c r="G363" t="n">
-        <v>781.540649414062</v>
+        <v>781.540588378906</v>
       </c>
       <c r="H363" t="n">
         <v>11</v>
@@ -11012,7 +11012,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G367" t="n">
-        <v>789.042663574219</v>
+        <v>789.042724609375</v>
       </c>
       <c r="H367" t="n">
         <v>81</v>
@@ -11099,7 +11099,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G370" t="n">
-        <v>776.686340332031</v>
+        <v>776.686401367188</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11157,7 +11157,7 @@
         <v>844.112976074219</v>
       </c>
       <c r="G372" t="n">
-        <v>781.540649414062</v>
+        <v>781.540588378906</v>
       </c>
       <c r="H372" t="n">
         <v>22</v>
@@ -11186,7 +11186,7 @@
         <v>847.449401855469</v>
       </c>
       <c r="G373" t="n">
-        <v>784.629699707031</v>
+        <v>784.629760742188</v>
       </c>
       <c r="H373" t="n">
         <v>28</v>
@@ -11215,7 +11215,7 @@
         <v>862.224914550781</v>
       </c>
       <c r="G374" t="n">
-        <v>798.309936523438</v>
+        <v>798.309997558594</v>
       </c>
       <c r="H374" t="n">
         <v>141</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.8603515625</v>
+        <v>767.860290527344</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -11447,7 +11447,7 @@
         <v>826.954284667969</v>
       </c>
       <c r="G382" t="n">
-        <v>765.653869628906</v>
+        <v>765.65380859375</v>
       </c>
       <c r="H382" t="n">
         <v>26</v>
@@ -11534,7 +11534,7 @@
         <v>822.18798828125</v>
       </c>
       <c r="G385" t="n">
-        <v>787.529846191406</v>
+        <v>787.52978515625</v>
       </c>
       <c r="H385" t="n">
         <v>11</v>
@@ -11563,7 +11563,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G386" t="n">
-        <v>784.790588378906</v>
+        <v>784.79052734375</v>
       </c>
       <c r="H386" t="n">
         <v>80</v>
@@ -11650,7 +11650,7 @@
         <v>806.935791015625</v>
       </c>
       <c r="G389" t="n">
-        <v>772.920532226562</v>
+        <v>772.920593261719</v>
       </c>
       <c r="H389" t="n">
         <v>91</v>
@@ -11766,7 +11766,7 @@
         <v>814.085266113281</v>
       </c>
       <c r="G393" t="n">
-        <v>779.768615722656</v>
+        <v>779.768737792969</v>
       </c>
       <c r="H393" t="n">
         <v>14</v>
@@ -11824,7 +11824,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G395" t="n">
-        <v>794.377868652344</v>
+        <v>794.377807617188</v>
       </c>
       <c r="H395" t="n">
         <v>100</v>
@@ -11853,7 +11853,7 @@
         <v>827.430908203125</v>
       </c>
       <c r="G396" t="n">
-        <v>792.551696777344</v>
+        <v>792.5517578125</v>
       </c>
       <c r="H396" t="n">
         <v>50</v>
@@ -11882,7 +11882,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G397" t="n">
-        <v>803.508666992188</v>
+        <v>803.508728027344</v>
       </c>
       <c r="H397" t="n">
         <v>472</v>
@@ -11911,7 +11911,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G398" t="n">
-        <v>803.508666992188</v>
+        <v>803.508728027344</v>
       </c>
       <c r="H398" t="n">
         <v>1</v>
@@ -11998,7 +11998,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G401" t="n">
-        <v>809.900268554688</v>
+        <v>809.900207519531</v>
       </c>
       <c r="H401" t="n">
         <v>3</v>
@@ -12027,7 +12027,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G402" t="n">
-        <v>809.900268554688</v>
+        <v>809.900207519531</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G403" t="n">
-        <v>809.900268554688</v>
+        <v>809.900207519531</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G404" t="n">
-        <v>809.900268554688</v>
+        <v>809.900207519531</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G405" t="n">
-        <v>794.377868652344</v>
+        <v>794.377807617188</v>
       </c>
       <c r="H405" t="n">
         <v>26</v>
@@ -12172,7 +12172,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G407" t="n">
-        <v>780.681701660156</v>
+        <v>780.681762695312</v>
       </c>
       <c r="H407" t="n">
         <v>176</v>
@@ -12288,7 +12288,7 @@
         <v>812.655334472656</v>
       </c>
       <c r="G411" t="n">
-        <v>778.398986816406</v>
+        <v>778.399047851562</v>
       </c>
       <c r="H411" t="n">
         <v>72</v>
@@ -12375,7 +12375,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G414" t="n">
-        <v>776.116271972656</v>
+        <v>776.116394042969</v>
       </c>
       <c r="H414" t="n">
         <v>102</v>
@@ -12404,7 +12404,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G415" t="n">
-        <v>776.116271972656</v>
+        <v>776.116394042969</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G416" t="n">
-        <v>780.681701660156</v>
+        <v>780.681762695312</v>
       </c>
       <c r="H416" t="n">
         <v>110</v>
@@ -12549,7 +12549,7 @@
         <v>865.084716796875</v>
       </c>
       <c r="G420" t="n">
-        <v>828.618286132812</v>
+        <v>828.618347167969</v>
       </c>
       <c r="H420" t="n">
         <v>44</v>
@@ -12578,7 +12578,7 @@
         <v>914.654296875</v>
       </c>
       <c r="G421" t="n">
-        <v>876.098327636719</v>
+        <v>876.098388671875</v>
       </c>
       <c r="H421" t="n">
         <v>26</v>
@@ -12636,7 +12636,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G423" t="n">
-        <v>858.293334960938</v>
+        <v>858.293395996094</v>
       </c>
       <c r="H423" t="n">
         <v>39</v>
@@ -12752,7 +12752,7 @@
         <v>895.112487792969</v>
       </c>
       <c r="G427" t="n">
-        <v>857.38037109375</v>
+        <v>857.380310058594</v>
       </c>
       <c r="H427" t="n">
         <v>253</v>
@@ -12781,7 +12781,7 @@
         <v>895.589111328125</v>
       </c>
       <c r="G428" t="n">
-        <v>857.836853027344</v>
+        <v>857.836791992188</v>
       </c>
       <c r="H428" t="n">
         <v>78</v>
@@ -12897,7 +12897,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G432" t="n">
-        <v>858.293334960938</v>
+        <v>858.293395996094</v>
       </c>
       <c r="H432" t="n">
         <v>12</v>
@@ -12926,7 +12926,7 @@
         <v>900.83203125</v>
       </c>
       <c r="G433" t="n">
-        <v>862.858703613281</v>
+        <v>862.858764648438</v>
       </c>
       <c r="H433" t="n">
         <v>7</v>
@@ -12984,7 +12984,7 @@
         <v>992.345153808594</v>
       </c>
       <c r="G435" t="n">
-        <v>950.514282226562</v>
+        <v>950.514221191406</v>
       </c>
       <c r="H435" t="n">
         <v>105</v>
@@ -13013,7 +13013,7 @@
         <v>984.719055175781</v>
       </c>
       <c r="G436" t="n">
-        <v>943.209594726562</v>
+        <v>943.209655761719</v>
       </c>
       <c r="H436" t="n">
         <v>184</v>
@@ -13071,7 +13071,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G438" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H438" t="n">
         <v>39</v>
@@ -13158,7 +13158,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G441" t="n">
-        <v>990.689636230469</v>
+        <v>990.689575195312</v>
       </c>
       <c r="H441" t="n">
         <v>59</v>
@@ -13216,7 +13216,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G443" t="n">
-        <v>1010.77740478516</v>
+        <v>1010.77734375</v>
       </c>
       <c r="H443" t="n">
         <v>187</v>
@@ -13245,7 +13245,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G444" t="n">
-        <v>1010.77740478516</v>
+        <v>1010.77734375</v>
       </c>
       <c r="H444" t="n">
         <v>22</v>
@@ -13361,7 +13361,7 @@
         <v>1051.44738769531</v>
       </c>
       <c r="G448" t="n">
-        <v>1007.12512207031</v>
+        <v>1007.12506103516</v>
       </c>
       <c r="H448" t="n">
         <v>61</v>
@@ -13419,7 +13419,7 @@
         <v>1047.63427734375</v>
       </c>
       <c r="G450" t="n">
-        <v>1003.47271728516</v>
+        <v>1003.47265625</v>
       </c>
       <c r="H450" t="n">
         <v>20</v>
@@ -13477,7 +13477,7 @@
         <v>1013.31689453125</v>
       </c>
       <c r="G452" t="n">
-        <v>970.601989746094</v>
+        <v>970.601928710938</v>
       </c>
       <c r="H452" t="n">
         <v>3</v>
@@ -13506,7 +13506,7 @@
         <v>1009.50384521484</v>
       </c>
       <c r="G453" t="n">
-        <v>966.949645996094</v>
+        <v>966.94970703125</v>
       </c>
       <c r="H453" t="n">
         <v>51</v>
@@ -13593,7 +13593,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G456" t="n">
-        <v>1013.51666259766</v>
+        <v>1013.5166015625</v>
       </c>
       <c r="H456" t="n">
         <v>14</v>
@@ -13622,7 +13622,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G457" t="n">
-        <v>1022.64752197266</v>
+        <v>1022.6474609375</v>
       </c>
       <c r="H457" t="n">
         <v>23</v>
@@ -13651,7 +13651,7 @@
         <v>1061.93322753906</v>
       </c>
       <c r="G458" t="n">
-        <v>1017.16888427734</v>
+        <v>1017.1689453125</v>
       </c>
       <c r="H458" t="n">
         <v>240</v>
@@ -13680,7 +13680,7 @@
         <v>1054.30712890625</v>
       </c>
       <c r="G459" t="n">
-        <v>1009.8642578125</v>
+        <v>1009.86437988281</v>
       </c>
       <c r="H459" t="n">
         <v>22</v>
@@ -13796,7 +13796,7 @@
         <v>1019.98968505859</v>
       </c>
       <c r="G463" t="n">
-        <v>976.993530273438</v>
+        <v>976.993469238281</v>
       </c>
       <c r="H463" t="n">
         <v>102</v>
@@ -13854,7 +13854,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G465" t="n">
-        <v>1022.64752197266</v>
+        <v>1022.6474609375</v>
       </c>
       <c r="H465" t="n">
         <v>176</v>
@@ -13883,7 +13883,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G466" t="n">
-        <v>1031.77807617188</v>
+        <v>1031.77819824219</v>
       </c>
       <c r="H466" t="n">
         <v>15</v>
@@ -13912,7 +13912,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G467" t="n">
-        <v>1013.51666259766</v>
+        <v>1013.5166015625</v>
       </c>
       <c r="H467" t="n">
         <v>33</v>
@@ -13970,7 +13970,7 @@
         <v>1088.62451171875</v>
       </c>
       <c r="G469" t="n">
-        <v>1042.73510742188</v>
+        <v>1042.73522949219</v>
       </c>
       <c r="H469" t="n">
         <v>50</v>
@@ -14028,7 +14028,7 @@
         <v>1083.85827636719</v>
       </c>
       <c r="G471" t="n">
-        <v>1038.16967773438</v>
+        <v>1038.16979980469</v>
       </c>
       <c r="H471" t="n">
         <v>11</v>
@@ -14057,7 +14057,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G472" t="n">
-        <v>1031.77807617188</v>
+        <v>1031.77819824219</v>
       </c>
       <c r="H472" t="n">
         <v>23</v>
@@ -14086,7 +14086,7 @@
         <v>1077.18542480469</v>
       </c>
       <c r="G473" t="n">
-        <v>1031.77807617188</v>
+        <v>1031.77819824219</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>1074.32556152344</v>
       </c>
       <c r="G475" t="n">
-        <v>1029.03881835938</v>
+        <v>1029.03894042969</v>
       </c>
       <c r="H475" t="n">
         <v>40</v>
@@ -14231,7 +14231,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G478" t="n">
-        <v>990.689636230469</v>
+        <v>990.689575195312</v>
       </c>
       <c r="H478" t="n">
         <v>72</v>
@@ -14260,7 +14260,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G479" t="n">
-        <v>990.689636230469</v>
+        <v>990.689575195312</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14289,7 +14289,7 @@
         <v>1003.78424072266</v>
       </c>
       <c r="G480" t="n">
-        <v>961.47119140625</v>
+        <v>961.471130371094</v>
       </c>
       <c r="H480" t="n">
         <v>14</v>
@@ -14405,7 +14405,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G484" t="n">
-        <v>903.947326660156</v>
+        <v>903.947265625</v>
       </c>
       <c r="H484" t="n">
         <v>51</v>
@@ -14434,7 +14434,7 @@
         <v>975.186401367188</v>
       </c>
       <c r="G485" t="n">
-        <v>934.078857421875</v>
+        <v>934.078796386719</v>
       </c>
       <c r="H485" t="n">
         <v>3</v>
@@ -14463,7 +14463,7 @@
         <v>975.186401367188</v>
       </c>
       <c r="G486" t="n">
-        <v>934.078857421875</v>
+        <v>934.078796386719</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G489" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H489" t="n">
         <v>1</v>
@@ -14608,7 +14608,7 @@
         <v>988.532104492188</v>
       </c>
       <c r="G491" t="n">
-        <v>946.861999511719</v>
+        <v>946.861938476562</v>
       </c>
       <c r="H491" t="n">
         <v>20</v>
@@ -14637,7 +14637,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G492" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H492" t="n">
         <v>36</v>
@@ -14956,7 +14956,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G503" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H503" t="n">
         <v>6</v>
@@ -14985,7 +14985,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G504" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G505" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G506" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H506" t="n">
         <v>147</v>
@@ -15072,7 +15072,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G507" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G508" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G509" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G510" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G511" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H511" t="n">
         <v>33</v>
@@ -15362,7 +15362,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G517" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H517" t="n">
         <v>3</v>
@@ -15449,7 +15449,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G520" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H520" t="n">
         <v>3</v>
@@ -15594,7 +15594,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G525" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H525" t="n">
         <v>7</v>
@@ -15623,7 +15623,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G526" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H526" t="n">
         <v>48</v>
@@ -15652,7 +15652,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G527" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H527" t="n">
         <v>51</v>
@@ -15681,7 +15681,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G528" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H528" t="n">
         <v>202</v>
@@ -15710,7 +15710,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G529" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H529" t="n">
         <v>3</v>
@@ -15739,7 +15739,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G530" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H530" t="n">
         <v>18</v>
@@ -15826,7 +15826,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G533" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H533" t="n">
         <v>11</v>
@@ -16000,7 +16000,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G539" t="n">
-        <v>903.947326660156</v>
+        <v>903.947265625</v>
       </c>
       <c r="H539" t="n">
         <v>1</v>
@@ -16029,7 +16029,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G540" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H540" t="n">
         <v>4</v>
@@ -16087,7 +16087,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G542" t="n">
-        <v>903.947326660156</v>
+        <v>903.947265625</v>
       </c>
       <c r="H542" t="n">
         <v>1</v>
@@ -16116,7 +16116,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G543" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H543" t="n">
         <v>1</v>
@@ -16406,7 +16406,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G553" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H553" t="n">
         <v>1</v>
@@ -16551,7 +16551,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G558" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H558" t="n">
         <v>72</v>
@@ -16609,7 +16609,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G560" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H560" t="n">
         <v>39</v>
@@ -16638,7 +16638,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G561" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H561" t="n">
         <v>7</v>
@@ -16667,7 +16667,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G562" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G563" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G564" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G565" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H565" t="n">
         <v>64</v>
@@ -16957,7 +16957,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G572" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H572" t="n">
         <v>14</v>
@@ -16986,7 +16986,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G573" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H573" t="n">
         <v>7</v>
@@ -17044,7 +17044,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G575" t="n">
-        <v>945.035766601562</v>
+        <v>945.035705566406</v>
       </c>
       <c r="H575" t="n">
         <v>15</v>
@@ -17276,7 +17276,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G583" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H583" t="n">
         <v>3</v>
@@ -17305,7 +17305,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G584" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H584" t="n">
         <v>129</v>
@@ -17334,7 +17334,7 @@
         <v>1005.69079589844</v>
       </c>
       <c r="G585" t="n">
-        <v>963.297302246094</v>
+        <v>963.29736328125</v>
       </c>
       <c r="H585" t="n">
         <v>4</v>
@@ -17740,7 +17740,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G599" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H599" t="n">
         <v>7</v>
@@ -17769,7 +17769,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G600" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H600" t="n">
         <v>1</v>
@@ -17798,7 +17798,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G601" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H601" t="n">
         <v>1</v>
@@ -17827,7 +17827,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G602" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H602" t="n">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G603" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G604" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H604" t="n">
         <v>3</v>
@@ -18088,7 +18088,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G611" t="n">
-        <v>990.689636230469</v>
+        <v>990.689575195312</v>
       </c>
       <c r="H611" t="n">
         <v>75</v>
@@ -18349,7 +18349,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G620" t="n">
-        <v>903.947326660156</v>
+        <v>903.947265625</v>
       </c>
       <c r="H620" t="n">
         <v>6</v>
@@ -18378,7 +18378,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G621" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H621" t="n">
         <v>7</v>
@@ -18407,7 +18407,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G622" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G623" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H623" t="n">
         <v>3</v>
@@ -18465,7 +18465,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G624" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G625" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H625" t="n">
         <v>4</v>
@@ -80067,6 +80067,35 @@
         <v>0</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G2" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G3" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -485,7 +485,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G4" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G5" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G6" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G7" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G8" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G9" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G10" t="n">
-        <v>599.072631835938</v>
+        <v>599.072692871094</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -688,7 +688,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G11" t="n">
-        <v>599.072631835938</v>
+        <v>599.072692871094</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G12" t="n">
-        <v>599.072631835938</v>
+        <v>599.072692871094</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G13" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G14" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G15" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G16" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G17" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G18" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G19" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G20" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G21" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G22" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1036,7 +1036,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G23" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G24" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G25" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G26" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>645.357971191406</v>
       </c>
       <c r="G27" t="n">
-        <v>573.65234375</v>
+        <v>573.652404785156</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -1181,7 +1181,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G28" t="n">
-        <v>567.720947265625</v>
+        <v>567.720886230469</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1529,7 +1529,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G40" t="n">
-        <v>555.010681152344</v>
+        <v>555.0107421875</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297180175781</v>
+        <v>567.297241210938</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>626.292724609375</v>
       </c>
       <c r="G62" t="n">
-        <v>556.705444335938</v>
+        <v>556.705383300781</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
@@ -2196,7 +2196,7 @@
         <v>664.899841308594</v>
       </c>
       <c r="G63" t="n">
-        <v>591.022827148438</v>
+        <v>591.02294921875</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -2225,7 +2225,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G64" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H64" t="n">
         <v>11</v>
@@ -2254,7 +2254,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G65" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G66" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G67" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G68" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G69" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G70" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G71" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G72" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G73" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G74" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G75" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G76" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G77" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>678.722106933594</v>
       </c>
       <c r="G78" t="n">
-        <v>603.309387207031</v>
+        <v>603.309326171875</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137878417969</v>
+        <v>618.137939453125</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G83" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H83" t="n">
         <v>39</v>
@@ -2805,7 +2805,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G84" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G85" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G86" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G87" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G88" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G89" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G90" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G91" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G92" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G93" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G94" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G95" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G96" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
@@ -3182,7 +3182,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G97" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G98" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G99" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G109" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H109" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G110" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G114" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G115" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G116" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G117" t="n">
-        <v>596.10693359375</v>
+        <v>596.106994628906</v>
       </c>
       <c r="H117" t="n">
         <v>3</v>
@@ -3791,7 +3791,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G118" t="n">
-        <v>596.10693359375</v>
+        <v>596.106994628906</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G119" t="n">
-        <v>596.10693359375</v>
+        <v>596.106994628906</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G121" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H121" t="n">
         <v>3</v>
@@ -3907,7 +3907,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G122" t="n">
-        <v>593.141296386719</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G127" t="n">
-        <v>576.1943359375</v>
+        <v>576.194396972656</v>
       </c>
       <c r="H127" t="n">
         <v>1</v>
@@ -4081,7 +4081,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G128" t="n">
-        <v>576.1943359375</v>
+        <v>576.194396972656</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G129" t="n">
-        <v>601.614685058594</v>
+        <v>601.61474609375</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
@@ -4139,7 +4139,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G130" t="n">
-        <v>604.579711914062</v>
+        <v>604.579650878906</v>
       </c>
       <c r="H130" t="n">
         <v>4</v>
@@ -4168,7 +4168,7 @@
         <v>652.984069824219</v>
       </c>
       <c r="G131" t="n">
-        <v>604.579711914062</v>
+        <v>604.579650878906</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G132" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G133" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G134" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G135" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G136" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G137" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G138" t="n">
-        <v>600.608032226562</v>
+        <v>600.608093261719</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G139" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H139" t="n">
         <v>1</v>
@@ -4429,7 +4429,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G140" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H140" t="n">
         <v>3</v>
@@ -4458,7 +4458,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G141" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>642.498168945312</v>
       </c>
       <c r="G142" t="n">
-        <v>594.871154785156</v>
+        <v>594.87109375</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G152" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G153" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G154" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G155" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G156" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G157" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G158" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G159" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G160" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G161" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G216" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H216" t="n">
         <v>18</v>
@@ -6662,7 +6662,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G217" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G218" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G219" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G220" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G221" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H221" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G222" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G223" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G224" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G225" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G226" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
@@ -6952,7 +6952,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G227" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G228" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G229" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G230" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G231" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G232" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.563110351562</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G259" t="n">
-        <v>553.389038085938</v>
+        <v>553.388916015625</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G260" t="n">
-        <v>553.389038085938</v>
+        <v>553.388916015625</v>
       </c>
       <c r="H260" t="n">
         <v>6</v>
@@ -7938,7 +7938,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G261" t="n">
-        <v>570.158325195312</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H261" t="n">
         <v>7</v>
@@ -7967,7 +7967,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G262" t="n">
-        <v>570.158325195312</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>615.806884765625</v>
       </c>
       <c r="G263" t="n">
-        <v>570.158325195312</v>
+        <v>570.158386230469</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G264" t="n">
-        <v>571.040954589844</v>
+        <v>571.041015625</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -8054,7 +8054,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G265" t="n">
-        <v>571.040954589844</v>
+        <v>571.041015625</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8112,7 +8112,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G267" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H267" t="n">
         <v>7</v>
@@ -8141,7 +8141,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G268" t="n">
-        <v>556.036865234375</v>
+        <v>556.036743164062</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G269" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H269" t="n">
         <v>1</v>
@@ -8199,7 +8199,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G270" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G271" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G272" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G273" t="n">
-        <v>551.623840332031</v>
+        <v>551.623779296875</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>601.984558105469</v>
       </c>
       <c r="G274" t="n">
-        <v>557.360717773438</v>
+        <v>557.360656738281</v>
       </c>
       <c r="H274" t="n">
         <v>7</v>
@@ -8402,7 +8402,7 @@
         <v>591.975341796875</v>
       </c>
       <c r="G277" t="n">
-        <v>548.093444824219</v>
+        <v>548.093383789062</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
@@ -8431,7 +8431,7 @@
         <v>591.022094726562</v>
       </c>
       <c r="G278" t="n">
-        <v>547.210815429688</v>
+        <v>547.210876464844</v>
       </c>
       <c r="H278" t="n">
         <v>15</v>
@@ -8837,7 +8837,7 @@
         <v>650.124267578125</v>
       </c>
       <c r="G292" t="n">
-        <v>601.931884765625</v>
+        <v>601.931945800781</v>
       </c>
       <c r="H292" t="n">
         <v>3</v>
@@ -8982,7 +8982,7 @@
         <v>634.8720703125</v>
       </c>
       <c r="G297" t="n">
-        <v>587.810363769531</v>
+        <v>587.810302734375</v>
       </c>
       <c r="H297" t="n">
         <v>26</v>
@@ -9011,7 +9011,7 @@
         <v>645.834594726562</v>
       </c>
       <c r="G298" t="n">
-        <v>597.960266113281</v>
+        <v>597.960205078125</v>
       </c>
       <c r="H298" t="n">
         <v>3</v>
@@ -9040,7 +9040,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G299" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H299" t="n">
         <v>4</v>
@@ -9069,7 +9069,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G300" t="n">
-        <v>600.166748046875</v>
+        <v>600.166687011719</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>665.37646484375</v>
       </c>
       <c r="G301" t="n">
-        <v>616.053466796875</v>
+        <v>616.053405761719</v>
       </c>
       <c r="H301" t="n">
         <v>17</v>
@@ -9156,7 +9156,7 @@
         <v>658.70361328125</v>
       </c>
       <c r="G303" t="n">
-        <v>609.875244140625</v>
+        <v>609.875305175781</v>
       </c>
       <c r="H303" t="n">
         <v>3</v>
@@ -9185,7 +9185,7 @@
         <v>655.3671875</v>
       </c>
       <c r="G304" t="n">
-        <v>606.786193847656</v>
+        <v>606.7861328125</v>
       </c>
       <c r="H304" t="n">
         <v>34</v>
@@ -9359,7 +9359,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G310" t="n">
-        <v>626.644714355469</v>
+        <v>626.644592285156</v>
       </c>
       <c r="H310" t="n">
         <v>7</v>
@@ -9446,7 +9446,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G313" t="n">
-        <v>626.644714355469</v>
+        <v>626.644592285156</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -9475,7 +9475,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G314" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H314" t="n">
         <v>39</v>
@@ -9504,7 +9504,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G315" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G316" t="n">
-        <v>636.794555664062</v>
+        <v>636.794494628906</v>
       </c>
       <c r="H316" t="n">
         <v>4</v>
@@ -9562,7 +9562,7 @@
         <v>687.778076171875</v>
       </c>
       <c r="G317" t="n">
-        <v>636.794555664062</v>
+        <v>636.794494628906</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>705.413452148438</v>
       </c>
       <c r="G320" t="n">
-        <v>653.12255859375</v>
+        <v>653.122619628906</v>
       </c>
       <c r="H320" t="n">
         <v>31</v>
@@ -9707,7 +9707,7 @@
         <v>714.946044921875</v>
       </c>
       <c r="G322" t="n">
-        <v>661.948547363281</v>
+        <v>661.948608398438</v>
       </c>
       <c r="H322" t="n">
         <v>9</v>
@@ -9852,7 +9852,7 @@
         <v>785.0107421875</v>
       </c>
       <c r="G327" t="n">
-        <v>726.819458007812</v>
+        <v>726.819519042969</v>
       </c>
       <c r="H327" t="n">
         <v>11</v>
@@ -9939,7 +9939,7 @@
         <v>781.674377441406</v>
       </c>
       <c r="G330" t="n">
-        <v>723.73046875</v>
+        <v>723.730529785156</v>
       </c>
       <c r="H330" t="n">
         <v>3</v>
@@ -9997,7 +9997,7 @@
         <v>787.393920898438</v>
       </c>
       <c r="G332" t="n">
-        <v>729.025939941406</v>
+        <v>729.026062011719</v>
       </c>
       <c r="H332" t="n">
         <v>22</v>
@@ -10026,7 +10026,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G333" t="n">
-        <v>726.378234863281</v>
+        <v>726.378173828125</v>
       </c>
       <c r="H333" t="n">
         <v>25</v>
@@ -10055,7 +10055,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G334" t="n">
-        <v>726.378234863281</v>
+        <v>726.378173828125</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G335" t="n">
-        <v>726.378234863281</v>
+        <v>726.378173828125</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>769.758605957031</v>
       </c>
       <c r="G336" t="n">
-        <v>712.697998046875</v>
+        <v>712.697937011719</v>
       </c>
       <c r="H336" t="n">
         <v>3</v>
@@ -10142,7 +10142,7 @@
         <v>769.758605957031</v>
       </c>
       <c r="G337" t="n">
-        <v>712.697998046875</v>
+        <v>712.697937011719</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G339" t="n">
-        <v>732.556396484375</v>
+        <v>732.556457519531</v>
       </c>
       <c r="H339" t="n">
         <v>15</v>
@@ -10229,7 +10229,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G340" t="n">
-        <v>732.556396484375</v>
+        <v>732.556457519531</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>799.786315917969</v>
       </c>
       <c r="G341" t="n">
-        <v>740.499755859375</v>
+        <v>740.499816894531</v>
       </c>
       <c r="H341" t="n">
         <v>6</v>
@@ -10316,7 +10316,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G343" t="n">
-        <v>758.593017578125</v>
+        <v>758.593078613281</v>
       </c>
       <c r="H343" t="n">
         <v>1</v>
@@ -10345,7 +10345,7 @@
         <v>822.664611816406</v>
       </c>
       <c r="G344" t="n">
-        <v>761.68212890625</v>
+        <v>761.682189941406</v>
       </c>
       <c r="H344" t="n">
         <v>18</v>
@@ -10374,7 +10374,7 @@
         <v>819.804809570312</v>
       </c>
       <c r="G345" t="n">
-        <v>759.034301757812</v>
+        <v>759.034423828125</v>
       </c>
       <c r="H345" t="n">
         <v>20</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10432,7 +10432,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G347" t="n">
-        <v>776.686401367188</v>
+        <v>776.686340332031</v>
       </c>
       <c r="H347" t="n">
         <v>15</v>
@@ -10461,7 +10461,7 @@
         <v>912.747802734375</v>
       </c>
       <c r="G348" t="n">
-        <v>845.087707519531</v>
+        <v>845.087646484375</v>
       </c>
       <c r="H348" t="n">
         <v>69</v>
@@ -10519,7 +10519,7 @@
         <v>924.66357421875</v>
       </c>
       <c r="G350" t="n">
-        <v>856.1201171875</v>
+        <v>856.120178222656</v>
       </c>
       <c r="H350" t="n">
         <v>99</v>
@@ -10635,7 +10635,7 @@
         <v>837.916748046875</v>
       </c>
       <c r="G354" t="n">
-        <v>775.803649902344</v>
+        <v>775.8037109375</v>
       </c>
       <c r="H354" t="n">
         <v>25</v>
@@ -10664,7 +10664,7 @@
         <v>845.066223144531</v>
       </c>
       <c r="G355" t="n">
-        <v>782.423217773438</v>
+        <v>782.423278808594</v>
       </c>
       <c r="H355" t="n">
         <v>31</v>
@@ -10751,7 +10751,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G358" t="n">
-        <v>789.042724609375</v>
+        <v>789.042663574219</v>
       </c>
       <c r="H358" t="n">
         <v>14</v>
@@ -10780,7 +10780,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G359" t="n">
-        <v>794.338256835938</v>
+        <v>794.338195800781</v>
       </c>
       <c r="H359" t="n">
         <v>1</v>
@@ -10838,7 +10838,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G361" t="n">
-        <v>794.338256835938</v>
+        <v>794.338195800781</v>
       </c>
       <c r="H361" t="n">
         <v>15</v>
@@ -10867,7 +10867,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G362" t="n">
-        <v>794.338256835938</v>
+        <v>794.338195800781</v>
       </c>
       <c r="H362" t="n">
         <v>22</v>
@@ -10925,7 +10925,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G364" t="n">
-        <v>794.338256835938</v>
+        <v>794.338195800781</v>
       </c>
       <c r="H364" t="n">
         <v>114</v>
@@ -10954,7 +10954,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G365" t="n">
-        <v>794.338256835938</v>
+        <v>794.338195800781</v>
       </c>
       <c r="H365" t="n">
         <v>67</v>
@@ -11012,7 +11012,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G367" t="n">
-        <v>789.042724609375</v>
+        <v>789.042663574219</v>
       </c>
       <c r="H367" t="n">
         <v>81</v>
@@ -11099,7 +11099,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G370" t="n">
-        <v>776.686401367188</v>
+        <v>776.686340332031</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>846.972778320312</v>
       </c>
       <c r="G371" t="n">
-        <v>784.188415527344</v>
+        <v>784.1884765625</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
@@ -11186,7 +11186,7 @@
         <v>847.449401855469</v>
       </c>
       <c r="G373" t="n">
-        <v>784.629760742188</v>
+        <v>784.629699707031</v>
       </c>
       <c r="H373" t="n">
         <v>28</v>
@@ -11215,7 +11215,7 @@
         <v>862.224914550781</v>
       </c>
       <c r="G374" t="n">
-        <v>798.309997558594</v>
+        <v>798.309936523438</v>
       </c>
       <c r="H374" t="n">
         <v>141</v>
@@ -11244,7 +11244,7 @@
         <v>856.50537109375</v>
       </c>
       <c r="G375" t="n">
-        <v>793.014404296875</v>
+        <v>793.014343261719</v>
       </c>
       <c r="H375" t="n">
         <v>17</v>
@@ -11302,7 +11302,7 @@
         <v>846.019470214844</v>
       </c>
       <c r="G377" t="n">
-        <v>783.305786132812</v>
+        <v>783.305725097656</v>
       </c>
       <c r="H377" t="n">
         <v>94</v>
@@ -11360,7 +11360,7 @@
         <v>824.094482421875</v>
       </c>
       <c r="G379" t="n">
-        <v>763.006042480469</v>
+        <v>763.005981445312</v>
       </c>
       <c r="H379" t="n">
         <v>259</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -11447,7 +11447,7 @@
         <v>826.954284667969</v>
       </c>
       <c r="G382" t="n">
-        <v>765.65380859375</v>
+        <v>765.653869628906</v>
       </c>
       <c r="H382" t="n">
         <v>26</v>
@@ -11563,7 +11563,7 @@
         <v>819.328186035156</v>
       </c>
       <c r="G386" t="n">
-        <v>784.79052734375</v>
+        <v>784.790588378906</v>
       </c>
       <c r="H386" t="n">
         <v>80</v>
@@ -11650,7 +11650,7 @@
         <v>806.935791015625</v>
       </c>
       <c r="G389" t="n">
-        <v>772.920593261719</v>
+        <v>772.920532226562</v>
       </c>
       <c r="H389" t="n">
         <v>91</v>
@@ -11679,7 +11679,7 @@
         <v>811.225463867188</v>
       </c>
       <c r="G390" t="n">
-        <v>777.029418945312</v>
+        <v>777.029357910156</v>
       </c>
       <c r="H390" t="n">
         <v>45</v>
@@ -11766,7 +11766,7 @@
         <v>814.085266113281</v>
       </c>
       <c r="G393" t="n">
-        <v>779.768737792969</v>
+        <v>779.768676757812</v>
       </c>
       <c r="H393" t="n">
         <v>14</v>
@@ -11853,7 +11853,7 @@
         <v>827.430908203125</v>
       </c>
       <c r="G396" t="n">
-        <v>792.5517578125</v>
+        <v>792.551696777344</v>
       </c>
       <c r="H396" t="n">
         <v>50</v>
@@ -11882,7 +11882,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G397" t="n">
-        <v>803.508728027344</v>
+        <v>803.508666992188</v>
       </c>
       <c r="H397" t="n">
         <v>472</v>
@@ -11911,7 +11911,7 @@
         <v>838.870056152344</v>
       </c>
       <c r="G398" t="n">
-        <v>803.508728027344</v>
+        <v>803.508666992188</v>
       </c>
       <c r="H398" t="n">
         <v>1</v>
@@ -12172,7 +12172,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G407" t="n">
-        <v>780.681762695312</v>
+        <v>780.681701660156</v>
       </c>
       <c r="H407" t="n">
         <v>176</v>
@@ -12201,7 +12201,7 @@
         <v>819.804809570312</v>
       </c>
       <c r="G408" t="n">
-        <v>785.2470703125</v>
+        <v>785.247131347656</v>
       </c>
       <c r="H408" t="n">
         <v>33</v>
@@ -12317,7 +12317,7 @@
         <v>809.318908691406</v>
       </c>
       <c r="G412" t="n">
-        <v>775.203247070312</v>
+        <v>775.203186035156</v>
       </c>
       <c r="H412" t="n">
         <v>39</v>
@@ -12346,7 +12346,7 @@
         <v>809.318908691406</v>
       </c>
       <c r="G413" t="n">
-        <v>775.203247070312</v>
+        <v>775.203186035156</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12375,7 +12375,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G414" t="n">
-        <v>776.116394042969</v>
+        <v>776.116333007812</v>
       </c>
       <c r="H414" t="n">
         <v>102</v>
@@ -12404,7 +12404,7 @@
         <v>810.272216796875</v>
       </c>
       <c r="G415" t="n">
-        <v>776.116394042969</v>
+        <v>776.116333007812</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -12433,7 +12433,7 @@
         <v>815.038513183594</v>
       </c>
       <c r="G416" t="n">
-        <v>780.681762695312</v>
+        <v>780.681701660156</v>
       </c>
       <c r="H416" t="n">
         <v>110</v>
@@ -12462,7 +12462,7 @@
         <v>819.804809570312</v>
       </c>
       <c r="G417" t="n">
-        <v>785.2470703125</v>
+        <v>785.247131347656</v>
       </c>
       <c r="H417" t="n">
         <v>42</v>
@@ -12636,7 +12636,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G423" t="n">
-        <v>858.293395996094</v>
+        <v>858.293334960938</v>
       </c>
       <c r="H423" t="n">
         <v>39</v>
@@ -12665,7 +12665,7 @@
         <v>901.308654785156</v>
       </c>
       <c r="G424" t="n">
-        <v>863.315307617188</v>
+        <v>863.315246582031</v>
       </c>
       <c r="H424" t="n">
         <v>11</v>
@@ -12694,7 +12694,7 @@
         <v>904.645080566406</v>
       </c>
       <c r="G425" t="n">
-        <v>866.511047363281</v>
+        <v>866.511108398438</v>
       </c>
       <c r="H425" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         <v>895.589111328125</v>
       </c>
       <c r="G428" t="n">
-        <v>857.836791992188</v>
+        <v>857.836853027344</v>
       </c>
       <c r="H428" t="n">
         <v>78</v>
@@ -12897,7 +12897,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G432" t="n">
-        <v>858.293395996094</v>
+        <v>858.293334960938</v>
       </c>
       <c r="H432" t="n">
         <v>12</v>
@@ -12955,7 +12955,7 @@
         <v>942.298889160156</v>
       </c>
       <c r="G434" t="n">
-        <v>902.577575683594</v>
+        <v>902.57763671875</v>
       </c>
       <c r="H434" t="n">
         <v>56</v>
@@ -13071,7 +13071,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G438" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H438" t="n">
         <v>39</v>
@@ -13158,7 +13158,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G441" t="n">
-        <v>990.689575195312</v>
+        <v>990.689636230469</v>
       </c>
       <c r="H441" t="n">
         <v>59</v>
@@ -13216,7 +13216,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G443" t="n">
-        <v>1010.77734375</v>
+        <v>1010.77740478516</v>
       </c>
       <c r="H443" t="n">
         <v>187</v>
@@ -13245,7 +13245,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G444" t="n">
-        <v>1010.77734375</v>
+        <v>1010.77740478516</v>
       </c>
       <c r="H444" t="n">
         <v>22</v>
@@ -13274,7 +13274,7 @@
         <v>1105.783203125</v>
       </c>
       <c r="G445" t="n">
-        <v>1059.17053222656</v>
+        <v>1059.17041015625</v>
       </c>
       <c r="H445" t="n">
         <v>103</v>
@@ -13361,7 +13361,7 @@
         <v>1051.44738769531</v>
       </c>
       <c r="G448" t="n">
-        <v>1007.12506103516</v>
+        <v>1007.12512207031</v>
       </c>
       <c r="H448" t="n">
         <v>61</v>
@@ -13419,7 +13419,7 @@
         <v>1047.63427734375</v>
       </c>
       <c r="G450" t="n">
-        <v>1003.47265625</v>
+        <v>1003.47271728516</v>
       </c>
       <c r="H450" t="n">
         <v>20</v>
@@ -13477,7 +13477,7 @@
         <v>1013.31689453125</v>
       </c>
       <c r="G452" t="n">
-        <v>970.601928710938</v>
+        <v>970.601989746094</v>
       </c>
       <c r="H452" t="n">
         <v>3</v>
@@ -13506,7 +13506,7 @@
         <v>1009.50384521484</v>
       </c>
       <c r="G453" t="n">
-        <v>966.94970703125</v>
+        <v>966.949645996094</v>
       </c>
       <c r="H453" t="n">
         <v>51</v>
@@ -13564,7 +13564,7 @@
         <v>1043.8212890625</v>
       </c>
       <c r="G455" t="n">
-        <v>999.820556640625</v>
+        <v>999.820495605469</v>
       </c>
       <c r="H455" t="n">
         <v>188</v>
@@ -13593,7 +13593,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G456" t="n">
-        <v>1013.5166015625</v>
+        <v>1013.51654052734</v>
       </c>
       <c r="H456" t="n">
         <v>14</v>
@@ -13622,7 +13622,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G457" t="n">
-        <v>1022.6474609375</v>
+        <v>1022.64739990234</v>
       </c>
       <c r="H457" t="n">
         <v>23</v>
@@ -13651,7 +13651,7 @@
         <v>1061.93322753906</v>
       </c>
       <c r="G458" t="n">
-        <v>1017.1689453125</v>
+        <v>1017.16888427734</v>
       </c>
       <c r="H458" t="n">
         <v>240</v>
@@ -13680,7 +13680,7 @@
         <v>1054.30712890625</v>
       </c>
       <c r="G459" t="n">
-        <v>1009.86437988281</v>
+        <v>1009.8642578125</v>
       </c>
       <c r="H459" t="n">
         <v>22</v>
@@ -13825,7 +13825,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G464" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H464" t="n">
         <v>61</v>
@@ -13854,7 +13854,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G465" t="n">
-        <v>1022.6474609375</v>
+        <v>1022.64739990234</v>
       </c>
       <c r="H465" t="n">
         <v>176</v>
@@ -13912,7 +13912,7 @@
         <v>1058.1201171875</v>
       </c>
       <c r="G467" t="n">
-        <v>1013.5166015625</v>
+        <v>1013.51654052734</v>
       </c>
       <c r="H467" t="n">
         <v>33</v>
@@ -13970,7 +13970,7 @@
         <v>1088.62451171875</v>
       </c>
       <c r="G469" t="n">
-        <v>1042.73522949219</v>
+        <v>1042.73510742188</v>
       </c>
       <c r="H469" t="n">
         <v>50</v>
@@ -14028,7 +14028,7 @@
         <v>1083.85827636719</v>
       </c>
       <c r="G471" t="n">
-        <v>1038.16979980469</v>
+        <v>1038.16967773438</v>
       </c>
       <c r="H471" t="n">
         <v>11</v>
@@ -14202,7 +14202,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G477" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H477" t="n">
         <v>22</v>
@@ -14231,7 +14231,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G478" t="n">
-        <v>990.689575195312</v>
+        <v>990.689636230469</v>
       </c>
       <c r="H478" t="n">
         <v>72</v>
@@ -14260,7 +14260,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G479" t="n">
-        <v>990.689575195312</v>
+        <v>990.689636230469</v>
       </c>
       <c r="H479" t="n">
         <v>0</v>
@@ -14376,7 +14376,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G483" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H483" t="n">
         <v>45</v>
@@ -14550,7 +14550,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G489" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H489" t="n">
         <v>1</v>
@@ -14637,7 +14637,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G492" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H492" t="n">
         <v>36</v>
@@ -14840,7 +14840,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G499" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H499" t="n">
         <v>22</v>
@@ -14898,7 +14898,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G501" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H501" t="n">
         <v>55</v>
@@ -14927,7 +14927,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G502" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G503" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H503" t="n">
         <v>6</v>
@@ -14985,7 +14985,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G504" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G505" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G506" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H506" t="n">
         <v>147</v>
@@ -15072,7 +15072,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G507" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G508" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G509" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G510" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G511" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H511" t="n">
         <v>33</v>
@@ -15362,7 +15362,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G517" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H517" t="n">
         <v>3</v>
@@ -15449,7 +15449,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G520" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H520" t="n">
         <v>3</v>
@@ -15594,7 +15594,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G525" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H525" t="n">
         <v>7</v>
@@ -15623,7 +15623,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G526" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H526" t="n">
         <v>48</v>
@@ -15652,7 +15652,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G527" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H527" t="n">
         <v>51</v>
@@ -15681,7 +15681,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G528" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H528" t="n">
         <v>202</v>
@@ -15710,7 +15710,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G529" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H529" t="n">
         <v>3</v>
@@ -15739,7 +15739,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G530" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H530" t="n">
         <v>18</v>
@@ -15826,7 +15826,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G533" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H533" t="n">
         <v>11</v>
@@ -15913,7 +15913,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G536" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H536" t="n">
         <v>28</v>
@@ -15942,7 +15942,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G537" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H537" t="n">
         <v>31</v>
@@ -15971,7 +15971,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G538" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H538" t="n">
         <v>62</v>
@@ -16029,7 +16029,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G540" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H540" t="n">
         <v>4</v>
@@ -16116,7 +16116,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G543" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H543" t="n">
         <v>1</v>
@@ -16145,7 +16145,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G544" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H544" t="n">
         <v>6</v>
@@ -16174,7 +16174,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G545" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H545" t="n">
         <v>39</v>
@@ -16203,7 +16203,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G546" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H546" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G547" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G548" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G550" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H550" t="n">
         <v>22</v>
@@ -16377,7 +16377,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G552" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H552" t="n">
         <v>14</v>
@@ -16406,7 +16406,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G553" t="n">
-        <v>917.643371582031</v>
+        <v>917.643432617188</v>
       </c>
       <c r="H553" t="n">
         <v>1</v>
@@ -16435,7 +16435,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G554" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H554" t="n">
         <v>168</v>
@@ -16551,7 +16551,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G558" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H558" t="n">
         <v>72</v>
@@ -16609,7 +16609,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G560" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H560" t="n">
         <v>39</v>
@@ -16638,7 +16638,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G561" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H561" t="n">
         <v>7</v>
@@ -16667,7 +16667,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G562" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G563" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H563" t="n">
         <v>0</v>
@@ -16725,7 +16725,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G564" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H564" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G565" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H565" t="n">
         <v>64</v>
@@ -16957,7 +16957,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G572" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H572" t="n">
         <v>14</v>
@@ -16986,7 +16986,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G573" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H573" t="n">
         <v>7</v>
@@ -17044,7 +17044,7 @@
         <v>986.625549316406</v>
       </c>
       <c r="G575" t="n">
-        <v>945.035705566406</v>
+        <v>945.035766601562</v>
       </c>
       <c r="H575" t="n">
         <v>15</v>
@@ -17276,7 +17276,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G583" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H583" t="n">
         <v>3</v>
@@ -17305,7 +17305,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G584" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H584" t="n">
         <v>129</v>
@@ -17334,7 +17334,7 @@
         <v>1005.69079589844</v>
       </c>
       <c r="G585" t="n">
-        <v>963.29736328125</v>
+        <v>963.297302246094</v>
       </c>
       <c r="H585" t="n">
         <v>4</v>
@@ -17363,7 +17363,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G586" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H586" t="n">
         <v>18</v>
@@ -17392,7 +17392,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G587" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G588" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G589" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G590" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G591" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G592" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G593" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G594" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G595" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G596" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G597" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G598" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G599" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H599" t="n">
         <v>7</v>
@@ -17769,7 +17769,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G600" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H600" t="n">
         <v>1</v>
@@ -17798,7 +17798,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G601" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H601" t="n">
         <v>1</v>
@@ -17827,7 +17827,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G602" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H602" t="n">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G603" t="n">
-        <v>940.470336914062</v>
+        <v>940.470397949219</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -17885,7 +17885,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G604" t="n">
-        <v>954.16650390625</v>
+        <v>954.166564941406</v>
       </c>
       <c r="H604" t="n">
         <v>3</v>
@@ -18001,7 +18001,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G608" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H608" t="n">
         <v>15</v>
@@ -18030,7 +18030,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G609" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G610" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18088,7 +18088,7 @@
         <v>1034.28857421875</v>
       </c>
       <c r="G611" t="n">
-        <v>990.689575195312</v>
+        <v>990.689636230469</v>
       </c>
       <c r="H611" t="n">
         <v>75</v>
@@ -18204,7 +18204,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G615" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H615" t="n">
         <v>3</v>
@@ -18233,7 +18233,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G616" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G618" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H618" t="n">
         <v>240</v>
@@ -18320,7 +18320,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G619" t="n">
-        <v>931.339660644531</v>
+        <v>931.339599609375</v>
       </c>
       <c r="H619" t="n">
         <v>12</v>
@@ -18378,7 +18378,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G621" t="n">
-        <v>917.643371582031</v>
+        <v>917.643432617188</v>
       </c>
       <c r="H621" t="n">
         <v>7</v>
@@ -18407,7 +18407,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G622" t="n">
-        <v>917.643371582031</v>
+        <v>917.643432617188</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G623" t="n">
-        <v>917.643371582031</v>
+        <v>917.643432617188</v>
       </c>
       <c r="H623" t="n">
         <v>3</v>
@@ -18465,7 +18465,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G624" t="n">
-        <v>917.643371582031</v>
+        <v>917.643432617188</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G625" t="n">
-        <v>922.208862304688</v>
+        <v>922.208801269531</v>
       </c>
       <c r="H625" t="n">
         <v>4</v>
@@ -18523,7 +18523,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G626" t="n">
-        <v>913.078002929688</v>
+        <v>913.078063964844</v>
       </c>
       <c r="H626" t="n">
         <v>18</v>
@@ -18552,7 +18552,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G627" t="n">
-        <v>925.736877441406</v>
+        <v>925.736938476562</v>
       </c>
       <c r="H627" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G628" t="n">
-        <v>925.736877441406</v>
+        <v>925.736938476562</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -18610,7 +18610,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G629" t="n">
-        <v>925.736877441406</v>
+        <v>925.736938476562</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -18726,7 +18726,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G633" t="n">
-        <v>925.736877441406</v>
+        <v>925.736938476562</v>
       </c>
       <c r="H633" t="n">
         <v>28</v>
@@ -18755,7 +18755,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G634" t="n">
-        <v>925.736877441406</v>
+        <v>925.736938476562</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G635" t="n">
-        <v>944.251708984375</v>
+        <v>944.251647949219</v>
       </c>
       <c r="H635" t="n">
         <v>3</v>
@@ -18813,7 +18813,7 @@
         <v>972.32666015625</v>
       </c>
       <c r="G636" t="n">
-        <v>944.251708984375</v>
+        <v>944.251647949219</v>
       </c>
       <c r="H636" t="n">
         <v>6</v>
@@ -18987,7 +18987,7 @@
         <v>949.448364257812</v>
       </c>
       <c r="G642" t="n">
-        <v>922.033935546875</v>
+        <v>922.033996582031</v>
       </c>
       <c r="H642" t="n">
         <v>4</v>
@@ -19016,7 +19016,7 @@
         <v>949.448364257812</v>
       </c>
       <c r="G643" t="n">
-        <v>922.033935546875</v>
+        <v>922.033996582031</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>949.448364257812</v>
       </c>
       <c r="G644" t="n">
-        <v>922.033935546875</v>
+        <v>922.033996582031</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
         <v>949.448364257812</v>
       </c>
       <c r="G645" t="n">
-        <v>922.033935546875</v>
+        <v>922.033996582031</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -19103,7 +19103,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G646" t="n">
-        <v>916.479614257812</v>
+        <v>916.479553222656</v>
       </c>
       <c r="H646" t="n">
         <v>69</v>
@@ -19132,7 +19132,7 @@
         <v>943.728820800781</v>
       </c>
       <c r="G647" t="n">
-        <v>916.479614257812</v>
+        <v>916.479553222656</v>
       </c>
       <c r="H647" t="n">
         <v>44</v>
@@ -80096,6 +80096,35 @@
         <v>0</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G2" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G3" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -485,7 +485,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G4" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G5" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G6" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G7" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G8" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G9" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G10" t="n">
-        <v>599.072692871094</v>
+        <v>599.072631835938</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -688,7 +688,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G11" t="n">
-        <v>599.072692871094</v>
+        <v>599.072631835938</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>673.955810546875</v>
       </c>
       <c r="G12" t="n">
-        <v>599.072692871094</v>
+        <v>599.072631835938</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G13" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G14" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G15" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G16" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G17" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G18" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G19" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G20" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G21" t="n">
-        <v>599.920043945312</v>
+        <v>599.919982910156</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G22" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1036,7 +1036,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G23" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G24" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G25" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G26" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>645.357971191406</v>
       </c>
       <c r="G27" t="n">
-        <v>573.652404785156</v>
+        <v>573.65234375</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -1181,7 +1181,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G28" t="n">
-        <v>567.720886230469</v>
+        <v>567.720947265625</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1326,7 +1326,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G33" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
@@ -1355,7 +1355,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G34" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G35" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G36" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G37" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G38" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G39" t="n">
-        <v>578.736328125</v>
+        <v>578.736389160156</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G41" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H41" t="n">
         <v>6</v>
@@ -1587,7 +1587,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G42" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G43" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H43" t="n">
         <v>7</v>
@@ -1645,7 +1645,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G44" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G45" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G46" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>636.778625488281</v>
       </c>
       <c r="G47" t="n">
-        <v>566.026245117188</v>
+        <v>566.026184082031</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297241210938</v>
+        <v>567.297302246094</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G55" t="n">
-        <v>584.667785644531</v>
+        <v>584.667846679688</v>
       </c>
       <c r="H55" t="n">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G56" t="n">
-        <v>584.667785644531</v>
+        <v>584.667846679688</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>626.292724609375</v>
       </c>
       <c r="G62" t="n">
-        <v>556.705383300781</v>
+        <v>556.705444335938</v>
       </c>
       <c r="H62" t="n">
         <v>1</v>
@@ -2196,7 +2196,7 @@
         <v>664.899841308594</v>
       </c>
       <c r="G63" t="n">
-        <v>591.02294921875</v>
+        <v>591.022888183594</v>
       </c>
       <c r="H63" t="n">
         <v>11</v>
@@ -2225,7 +2225,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G64" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H64" t="n">
         <v>11</v>
@@ -2254,7 +2254,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G65" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G66" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G67" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G68" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G69" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G70" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G71" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G72" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G73" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G74" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G75" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G76" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G77" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>678.722106933594</v>
       </c>
       <c r="G78" t="n">
-        <v>603.309326171875</v>
+        <v>603.309387207031</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2660,7 +2660,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G79" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H79" t="n">
         <v>1</v>
@@ -2689,7 +2689,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G80" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G81" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>695.404174804688</v>
       </c>
       <c r="G82" t="n">
-        <v>618.137939453125</v>
+        <v>618.137878417969</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G83" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H83" t="n">
         <v>39</v>
@@ -2805,7 +2805,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G84" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G85" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G86" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G87" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G88" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G89" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G90" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G91" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G92" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G93" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G94" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G95" t="n">
-        <v>610.088134765625</v>
+        <v>610.088195800781</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G96" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H96" t="n">
         <v>6</v>
@@ -3182,7 +3182,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G97" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G98" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G99" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G100" t="n">
-        <v>584.667785644531</v>
+        <v>584.667846679688</v>
       </c>
       <c r="H100" t="n">
         <v>9</v>
@@ -3298,7 +3298,7 @@
         <v>690.161254882812</v>
       </c>
       <c r="G101" t="n">
-        <v>613.477600097656</v>
+        <v>613.4775390625</v>
       </c>
       <c r="H101" t="n">
         <v>40</v>
@@ -3530,7 +3530,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G109" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H109" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G110" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G114" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G115" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G116" t="n">
-        <v>596.954345703125</v>
+        <v>596.954284667969</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G117" t="n">
-        <v>596.106994628906</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H117" t="n">
         <v>3</v>
@@ -3791,7 +3791,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G118" t="n">
-        <v>596.106994628906</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>670.619384765625</v>
       </c>
       <c r="G119" t="n">
-        <v>596.106994628906</v>
+        <v>596.10693359375</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G121" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H121" t="n">
         <v>3</v>
@@ -3907,7 +3907,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G122" t="n">
-        <v>593.141235351562</v>
+        <v>593.141174316406</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G129" t="n">
-        <v>601.61474609375</v>
+        <v>601.614685058594</v>
       </c>
       <c r="H129" t="n">
         <v>15</v>
@@ -4197,7 +4197,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G132" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G133" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G134" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G135" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G136" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G137" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G138" t="n">
-        <v>600.608093261719</v>
+        <v>600.608032226562</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G139" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H139" t="n">
         <v>1</v>
@@ -4777,7 +4777,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G152" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G153" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G154" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G155" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G156" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G157" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G158" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G159" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G160" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G161" t="n">
-        <v>575.0126953125</v>
+        <v>575.012634277344</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G198" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H198" t="n">
         <v>7</v>
@@ -6140,7 +6140,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G199" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G200" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G201" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G202" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G203" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G204" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G205" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H205" t="n">
         <v>12</v>
@@ -6343,7 +6343,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G206" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H206" t="n">
         <v>1</v>
@@ -6372,7 +6372,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G207" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G208" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G209" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G210" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G211" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G212" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G213" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G214" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G215" t="n">
-        <v>582.514709472656</v>
+        <v>582.514770507812</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G216" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H216" t="n">
         <v>18</v>
@@ -6662,7 +6662,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G217" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G218" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G219" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G220" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G221" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H221" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G222" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G223" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G224" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G225" t="n">
-        <v>563.980224609375</v>
+        <v>563.980163574219</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G226" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
@@ -6952,7 +6952,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G227" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G228" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G229" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G230" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G231" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G232" t="n">
-        <v>538.384765625</v>
+        <v>538.384826660156</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.56298828125</v>
+        <v>544.563049316406</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G240" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H240" t="n">
         <v>7</v>
@@ -7358,7 +7358,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G241" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G242" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G243" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G244" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G245" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H245" t="n">
         <v>193</v>
@@ -7503,7 +7503,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G246" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G247" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G248" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G249" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G250" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G251" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G252" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G253" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G254" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G255" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G256" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G257" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G258" t="n">
-        <v>543.680480957031</v>
+        <v>543.680419921875</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G259" t="n">
-        <v>553.388916015625</v>
+        <v>553.389038085938</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G260" t="n">
-        <v>553.388916015625</v>
+        <v>553.389038085938</v>
       </c>
       <c r="H260" t="n">
         <v>6</v>
@@ -8025,7 +8025,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G264" t="n">
-        <v>571.041015625</v>
+        <v>571.040954589844</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -8054,7 +8054,7 @@
         <v>616.760131835938</v>
       </c>
       <c r="G265" t="n">
-        <v>571.041015625</v>
+        <v>571.040954589844</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8112,7 +8112,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G267" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H267" t="n">
         <v>7</v>
@@ -8141,7 +8141,7 @@
         <v>600.5546875</v>
       </c>
       <c r="G268" t="n">
-        <v>556.036743164062</v>
+        <v>556.036804199219</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G269" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H269" t="n">
         <v>1</v>
@@ -8199,7 +8199,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G270" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G271" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G272" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>595.788391113281</v>
       </c>
       <c r="G273" t="n">
-        <v>551.623779296875</v>
+        <v>551.623840332031</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>601.984558105469</v>
       </c>
       <c r="G274" t="n">
-        <v>557.360656738281</v>
+        <v>557.360717773438</v>
       </c>
       <c r="H274" t="n">
         <v>7</v>
@@ -8344,7 +8344,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G275" t="n">
-        <v>557.802001953125</v>
+        <v>557.801940917969</v>
       </c>
       <c r="H275" t="n">
         <v>1</v>
@@ -8373,7 +8373,7 @@
         <v>602.461181640625</v>
       </c>
       <c r="G276" t="n">
-        <v>557.802001953125</v>
+        <v>557.801940917969</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>591.975341796875</v>
       </c>
       <c r="G277" t="n">
-        <v>548.093383789062</v>
+        <v>548.093444824219</v>
       </c>
       <c r="H277" t="n">
         <v>6</v>
@@ -8431,7 +8431,7 @@
         <v>591.022094726562</v>
       </c>
       <c r="G278" t="n">
-        <v>547.210876464844</v>
+        <v>547.210815429688</v>
       </c>
       <c r="H278" t="n">
         <v>15</v>
@@ -8489,7 +8489,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G280" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H280" t="n">
         <v>9</v>
@@ -8518,7 +8518,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G281" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G282" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G283" t="n">
-        <v>564.862731933594</v>
+        <v>564.86279296875</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>645.834594726562</v>
       </c>
       <c r="G298" t="n">
-        <v>597.960205078125</v>
+        <v>597.960144042969</v>
       </c>
       <c r="H298" t="n">
         <v>3</v>
@@ -9040,7 +9040,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G299" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H299" t="n">
         <v>4</v>
@@ -9069,7 +9069,7 @@
         <v>648.2177734375</v>
       </c>
       <c r="G300" t="n">
-        <v>600.166687011719</v>
+        <v>600.166748046875</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>665.37646484375</v>
       </c>
       <c r="G301" t="n">
-        <v>616.053405761719</v>
+        <v>616.053466796875</v>
       </c>
       <c r="H301" t="n">
         <v>17</v>
@@ -9156,7 +9156,7 @@
         <v>658.70361328125</v>
       </c>
       <c r="G303" t="n">
-        <v>609.875305175781</v>
+        <v>609.875244140625</v>
       </c>
       <c r="H303" t="n">
         <v>3</v>
@@ -9359,7 +9359,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G310" t="n">
-        <v>626.644592285156</v>
+        <v>626.644653320312</v>
       </c>
       <c r="H310" t="n">
         <v>7</v>
@@ -9446,7 +9446,7 @@
         <v>676.815612792969</v>
       </c>
       <c r="G313" t="n">
-        <v>626.644592285156</v>
+        <v>626.644653320312</v>
       </c>
       <c r="H313" t="n">
         <v>6</v>
@@ -9475,7 +9475,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G314" t="n">
-        <v>636.353149414062</v>
+        <v>636.353210449219</v>
       </c>
       <c r="H314" t="n">
         <v>39</v>
@@ -9504,7 +9504,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G315" t="n">
-        <v>636.353149414062</v>
+        <v>636.353210449219</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>712.562927246094</v>
       </c>
       <c r="G319" t="n">
-        <v>659.742065429688</v>
+        <v>659.742126464844</v>
       </c>
       <c r="H319" t="n">
         <v>42</v>
@@ -9649,7 +9649,7 @@
         <v>705.413452148438</v>
       </c>
       <c r="G320" t="n">
-        <v>653.122619628906</v>
+        <v>653.12255859375</v>
       </c>
       <c r="H320" t="n">
         <v>31</v>
@@ -9678,7 +9678,7 @@
         <v>700.647155761719</v>
       </c>
       <c r="G321" t="n">
-        <v>648.709594726562</v>
+        <v>648.709655761719</v>
       </c>
       <c r="H321" t="n">
         <v>9</v>
@@ -9794,7 +9794,7 @@
         <v>756.889587402344</v>
       </c>
       <c r="G325" t="n">
-        <v>700.782958984375</v>
+        <v>700.783020019531</v>
       </c>
       <c r="H325" t="n">
         <v>4</v>
@@ -9852,7 +9852,7 @@
         <v>785.0107421875</v>
       </c>
       <c r="G327" t="n">
-        <v>726.819519042969</v>
+        <v>726.819458007812</v>
       </c>
       <c r="H327" t="n">
         <v>11</v>
@@ -9881,7 +9881,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G328" t="n">
-        <v>741.382385253906</v>
+        <v>741.38232421875</v>
       </c>
       <c r="H328" t="n">
         <v>34</v>
@@ -9910,7 +9910,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G329" t="n">
-        <v>741.382385253906</v>
+        <v>741.38232421875</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G333" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H333" t="n">
         <v>25</v>
@@ -10055,7 +10055,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G334" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>784.534118652344</v>
       </c>
       <c r="G335" t="n">
-        <v>726.378173828125</v>
+        <v>726.378234863281</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>822.664611816406</v>
       </c>
       <c r="G344" t="n">
-        <v>761.682189941406</v>
+        <v>761.68212890625</v>
       </c>
       <c r="H344" t="n">
         <v>18</v>
@@ -10374,7 +10374,7 @@
         <v>819.804809570312</v>
       </c>
       <c r="G345" t="n">
-        <v>759.034423828125</v>
+        <v>759.034362792969</v>
       </c>
       <c r="H345" t="n">
         <v>20</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.8603515625</v>
+        <v>767.860290527344</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10461,7 +10461,7 @@
         <v>912.747802734375</v>
       </c>
       <c r="G348" t="n">
-        <v>845.087646484375</v>
+        <v>845.087707519531</v>
       </c>
       <c r="H348" t="n">
         <v>69</v>
@@ -10519,7 +10519,7 @@
         <v>924.66357421875</v>
       </c>
       <c r="G350" t="n">
-        <v>856.120178222656</v>
+        <v>856.1201171875</v>
       </c>
       <c r="H350" t="n">
         <v>99</v>
@@ -10664,7 +10664,7 @@
         <v>845.066223144531</v>
       </c>
       <c r="G355" t="n">
-        <v>782.423278808594</v>
+        <v>782.423217773438</v>
       </c>
       <c r="H355" t="n">
         <v>31</v>
@@ -10751,7 +10751,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G358" t="n">
-        <v>789.042663574219</v>
+        <v>789.042724609375</v>
       </c>
       <c r="H358" t="n">
         <v>14</v>
@@ -10780,7 +10780,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G359" t="n">
-        <v>794.338195800781</v>
+        <v>794.338256835938</v>
       </c>
       <c r="H359" t="n">
         <v>1</v>
@@ -10809,7 +10809,7 @@
         <v>867.467895507812</v>
       </c>
       <c r="G360" t="n">
-        <v>803.164306640625</v>
+        <v>803.164245605469</v>
       </c>
       <c r="H360" t="n">
         <v>47</v>
@@ -10838,7 +10838,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G361" t="n">
-        <v>794.338195800781</v>
+        <v>794.338256835938</v>
       </c>
       <c r="H361" t="n">
         <v>15</v>
@@ -10867,7 +10867,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G362" t="n">
-        <v>794.338195800781</v>
+        <v>794.338256835938</v>
       </c>
       <c r="H362" t="n">
         <v>22</v>
@@ -10925,7 +10925,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G364" t="n">
-        <v>794.338195800781</v>
+        <v>794.338256835938</v>
       </c>
       <c r="H364" t="n">
         <v>114</v>
@@ -10954,7 +10954,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G365" t="n">
-        <v>794.338195800781</v>
+        <v>794.338256835938</v>
       </c>
       <c r="H365" t="n">
         <v>67</v>
@@ -11012,7 +11012,7 @@
         <v>852.215698242188</v>
       </c>
       <c r="G367" t="n">
-        <v>789.042663574219</v>
+        <v>789.042724609375</v>
       </c>
       <c r="H367" t="n">
         <v>81</v>
@@ -11128,7 +11128,7 @@
         <v>846.972778320312</v>
       </c>
       <c r="G371" t="n">
-        <v>784.1884765625</v>
+        <v>784.188415527344</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
@@ -11186,7 +11186,7 @@
         <v>847.449401855469</v>
       </c>
       <c r="G373" t="n">
-        <v>784.629699707031</v>
+        <v>784.629638671875</v>
       </c>
       <c r="H373" t="n">
         <v>28</v>
@@ -11215,7 +11215,7 @@
         <v>862.224914550781</v>
       </c>
       <c r="G374" t="n">
-        <v>798.309936523438</v>
+        <v>798.309997558594</v>
       </c>
       <c r="H374" t="n">
         <v>141</v>
@@ -11302,7 +11302,7 @@
         <v>846.019470214844</v>
       </c>
       <c r="G377" t="n">
-        <v>783.305725097656</v>
+        <v>783.305786132812</v>
       </c>
       <c r="H377" t="n">
         <v>94</v>
@@ -11331,7 +11331,7 @@
         <v>840.776550292969</v>
       </c>
       <c r="G378" t="n">
-        <v>778.451538085938</v>
+        <v>778.451477050781</v>
       </c>
       <c r="H378" t="n">
         <v>7</v>
@@ -11360,7 +11360,7 @@
         <v>824.094482421875</v>
       </c>
       <c r="G379" t="n">
-        <v>763.005981445312</v>
+        <v>763.006042480469</v>
       </c>
       <c r="H379" t="n">
         <v>259</v>
@@ -11389,7 +11389,7 @@
         <v>827.907531738281</v>
       </c>
       <c r="G380" t="n">
-        <v>766.536437988281</v>
+        <v>766.536499023438</v>
       </c>
       <c r="H380" t="n">
         <v>36</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.8603515625</v>
+        <v>767.860290527344</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -11592,7 +11592,7 @@
         <v>795.973266601562</v>
       </c>
       <c r="G387" t="n">
-        <v>762.420104980469</v>
+        <v>762.420166015625</v>
       </c>
       <c r="H387" t="n">
         <v>140</v>
@@ -11795,7 +11795,7 @@
         <v>827.907531738281</v>
       </c>
       <c r="G394" t="n">
-        <v>793.008239746094</v>
+        <v>793.00830078125</v>
       </c>
       <c r="H394" t="n">
         <v>99</v>
@@ -11853,7 +11853,7 @@
         <v>827.430908203125</v>
       </c>
       <c r="G396" t="n">
-        <v>792.551696777344</v>
+        <v>792.5517578125</v>
       </c>
       <c r="H396" t="n">
         <v>50</v>
@@ -11940,7 +11940,7 @@
         <v>850.785827636719</v>
       </c>
       <c r="G399" t="n">
-        <v>814.922180175781</v>
+        <v>814.922119140625</v>
       </c>
       <c r="H399" t="n">
         <v>9</v>
@@ -11969,7 +11969,7 @@
         <v>850.785827636719</v>
       </c>
       <c r="G400" t="n">
-        <v>814.922180175781</v>
+        <v>814.922119140625</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -12143,7 +12143,7 @@
         <v>834.103759765625</v>
       </c>
       <c r="G406" t="n">
-        <v>798.943298339844</v>
+        <v>798.943359375</v>
       </c>
       <c r="H406" t="n">
         <v>129</v>
@@ -12230,7 +12230,7 @@
         <v>824.571105957031</v>
       </c>
       <c r="G409" t="n">
-        <v>789.812438964844</v>
+        <v>789.8125</v>
       </c>
       <c r="H409" t="n">
         <v>100</v>
@@ -12317,7 +12317,7 @@
         <v>809.318908691406</v>
       </c>
       <c r="G412" t="n">
-        <v>775.203186035156</v>
+        <v>775.203247070312</v>
       </c>
       <c r="H412" t="n">
         <v>39</v>
@@ -12346,7 +12346,7 @@
         <v>809.318908691406</v>
       </c>
       <c r="G413" t="n">
-        <v>775.203186035156</v>
+        <v>775.203247070312</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G423" t="n">
-        <v>858.293334960938</v>
+        <v>858.293395996094</v>
       </c>
       <c r="H423" t="n">
         <v>39</v>
@@ -12723,7 +12723,7 @@
         <v>923.710327148438</v>
       </c>
       <c r="G426" t="n">
-        <v>884.772583007812</v>
+        <v>884.772644042969</v>
       </c>
       <c r="H426" t="n">
         <v>53</v>
@@ -12897,7 +12897,7 @@
         <v>896.065734863281</v>
       </c>
       <c r="G432" t="n">
-        <v>858.293334960938</v>
+        <v>858.293395996094</v>
       </c>
       <c r="H432" t="n">
         <v>12</v>
@@ -12955,7 +12955,7 @@
         <v>942.298889160156</v>
       </c>
       <c r="G434" t="n">
-        <v>902.57763671875</v>
+        <v>902.577697753906</v>
       </c>
       <c r="H434" t="n">
         <v>56</v>
@@ -13042,7 +13042,7 @@
         <v>954.214660644531</v>
       </c>
       <c r="G437" t="n">
-        <v>913.991149902344</v>
+        <v>913.991088867188</v>
       </c>
       <c r="H437" t="n">
         <v>118</v>
@@ -13187,7 +13187,7 @@
         <v>1066.69946289062</v>
       </c>
       <c r="G442" t="n">
-        <v>1021.73425292969</v>
+        <v>1021.73431396484</v>
       </c>
       <c r="H442" t="n">
         <v>25</v>
@@ -13216,7 +13216,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G443" t="n">
-        <v>1010.77740478516</v>
+        <v>1010.77746582031</v>
       </c>
       <c r="H443" t="n">
         <v>187</v>
@@ -13245,7 +13245,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G444" t="n">
-        <v>1010.77740478516</v>
+        <v>1010.77746582031</v>
       </c>
       <c r="H444" t="n">
         <v>22</v>
@@ -13390,7 +13390,7 @@
         <v>1057.16687011719</v>
       </c>
       <c r="G449" t="n">
-        <v>1012.603515625</v>
+        <v>1012.60345458984</v>
       </c>
       <c r="H449" t="n">
         <v>39</v>
@@ -13419,7 +13419,7 @@
         <v>1047.63427734375</v>
       </c>
       <c r="G450" t="n">
-        <v>1003.47271728516</v>
+        <v>1003.47277832031</v>
       </c>
       <c r="H450" t="n">
         <v>20</v>
@@ -13448,7 +13448,7 @@
         <v>1035.24194335938</v>
       </c>
       <c r="G451" t="n">
-        <v>991.602783203125</v>
+        <v>991.602844238281</v>
       </c>
       <c r="H451" t="n">
         <v>12</v>
@@ -13535,7 +13535,7 @@
         <v>1037.1484375</v>
       </c>
       <c r="G454" t="n">
-        <v>993.428894042969</v>
+        <v>993.428955078125</v>
       </c>
       <c r="H454" t="n">
         <v>39</v>
@@ -13622,7 +13622,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G457" t="n">
-        <v>1022.64739990234</v>
+        <v>1022.6474609375</v>
       </c>
       <c r="H457" t="n">
         <v>23</v>
@@ -13680,7 +13680,7 @@
         <v>1054.30712890625</v>
       </c>
       <c r="G459" t="n">
-        <v>1009.8642578125</v>
+        <v>1009.86431884766</v>
       </c>
       <c r="H459" t="n">
         <v>22</v>
@@ -13709,7 +13709,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G460" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H460" t="n">
         <v>221</v>
@@ -13738,7 +13738,7 @@
         <v>1024.75598144531</v>
       </c>
       <c r="G461" t="n">
-        <v>981.558898925781</v>
+        <v>981.558837890625</v>
       </c>
       <c r="H461" t="n">
         <v>69</v>
@@ -13825,7 +13825,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G464" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H464" t="n">
         <v>61</v>
@@ -13854,7 +13854,7 @@
         <v>1067.65283203125</v>
       </c>
       <c r="G465" t="n">
-        <v>1022.64739990234</v>
+        <v>1022.6474609375</v>
       </c>
       <c r="H465" t="n">
         <v>176</v>
@@ -14028,7 +14028,7 @@
         <v>1083.85827636719</v>
       </c>
       <c r="G471" t="n">
-        <v>1038.16967773438</v>
+        <v>1038.16979980469</v>
       </c>
       <c r="H471" t="n">
         <v>11</v>
@@ -14202,7 +14202,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G477" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H477" t="n">
         <v>22</v>
@@ -14492,7 +14492,7 @@
         <v>950.878234863281</v>
       </c>
       <c r="G487" t="n">
-        <v>910.795288085938</v>
+        <v>910.795349121094</v>
       </c>
       <c r="H487" t="n">
         <v>12</v>
@@ -14521,7 +14521,7 @@
         <v>958.98095703125</v>
       </c>
       <c r="G488" t="n">
-        <v>918.556518554688</v>
+        <v>918.556457519531</v>
       </c>
       <c r="H488" t="n">
         <v>1</v>
@@ -14579,7 +14579,7 @@
         <v>995.204895019531</v>
       </c>
       <c r="G490" t="n">
-        <v>953.25341796875</v>
+        <v>953.253479003906</v>
       </c>
       <c r="H490" t="n">
         <v>3</v>
@@ -14666,7 +14666,7 @@
         <v>985.672302246094</v>
       </c>
       <c r="G493" t="n">
-        <v>944.122680664062</v>
+        <v>944.122741699219</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14811,7 +14811,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G498" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H498" t="n">
         <v>6</v>
@@ -15391,7 +15391,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G518" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H518" t="n">
         <v>20</v>
@@ -15420,7 +15420,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G519" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G521" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H521" t="n">
         <v>166</v>
@@ -15507,7 +15507,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G522" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G523" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H523" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G524" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G525" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H525" t="n">
         <v>7</v>
@@ -15768,7 +15768,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G531" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H531" t="n">
         <v>47</v>
@@ -15797,7 +15797,7 @@
         <v>1000.92449951172</v>
       </c>
       <c r="G532" t="n">
-        <v>958.73193359375</v>
+        <v>958.731994628906</v>
       </c>
       <c r="H532" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G541" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H541" t="n">
         <v>1</v>
@@ -16290,7 +16290,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G549" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H549" t="n">
         <v>23</v>
@@ -17073,7 +17073,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G576" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H576" t="n">
         <v>56</v>
@@ -17276,7 +17276,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G583" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H583" t="n">
         <v>3</v>
@@ -17305,7 +17305,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G584" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H584" t="n">
         <v>129</v>
@@ -17363,7 +17363,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G586" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H586" t="n">
         <v>18</v>
@@ -17392,7 +17392,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G587" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G588" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G589" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G590" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G591" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G592" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G593" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G594" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G595" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G596" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G597" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G598" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17740,7 +17740,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G599" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H599" t="n">
         <v>7</v>
@@ -17885,7 +17885,7 @@
         <v>996.158142089844</v>
       </c>
       <c r="G604" t="n">
-        <v>954.166564941406</v>
+        <v>954.16650390625</v>
       </c>
       <c r="H604" t="n">
         <v>3</v>
@@ -18001,7 +18001,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G608" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H608" t="n">
         <v>15</v>
@@ -18030,7 +18030,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G609" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G610" t="n">
-        <v>986.124328613281</v>
+        <v>986.124267578125</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>967.560302734375</v>
       </c>
       <c r="G614" t="n">
-        <v>926.774230957031</v>
+        <v>926.774169921875</v>
       </c>
       <c r="H614" t="n">
         <v>67</v>
@@ -80125,6 +80125,35 @@
         <v>0</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ABC.MI.xlsx
+++ b/data/ABC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G2" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G3" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -485,7 +485,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G4" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G5" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G6" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G7" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G8" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G9" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G13" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -775,7 +775,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G14" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G15" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G16" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G17" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G18" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G19" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G20" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>674.909057617188</v>
       </c>
       <c r="G21" t="n">
-        <v>599.919982910156</v>
+        <v>599.920043945312</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G22" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1036,7 +1036,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G23" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G24" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G25" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G26" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G29" t="n">
-        <v>551.621398925781</v>
+        <v>551.621276855469</v>
       </c>
       <c r="H29" t="n">
         <v>20</v>
@@ -1239,7 +1239,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G30" t="n">
-        <v>551.621398925781</v>
+        <v>551.621276855469</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G31" t="n">
-        <v>551.621398925781</v>
+        <v>551.621276855469</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>620.573181152344</v>
       </c>
       <c r="G32" t="n">
-        <v>551.621398925781</v>
+        <v>551.621276855469</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G33" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H33" t="n">
         <v>6</v>
@@ -1355,7 +1355,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G34" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G35" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G36" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G37" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G38" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>651.077514648438</v>
       </c>
       <c r="G39" t="n">
-        <v>578.736389160156</v>
+        <v>578.736328125</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G40" t="n">
-        <v>555.0107421875</v>
+        <v>555.010803222656</v>
       </c>
       <c r="H40" t="n">
         <v>6</v>
@@ -1761,7 +1761,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G48" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G49" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G50" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G51" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G52" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G53" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>638.20849609375</v>
       </c>
       <c r="G54" t="n">
-        <v>567.297302246094</v>
+        <v>567.297180175781</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G55" t="n">
-        <v>584.667846679688</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H55" t="n">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G56" t="n">
-        <v>584.667846679688</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>678.722106933594</v>
       </c>
       <c r="G78" t="n">
-        <v>603.309387207031</v>
+        <v>603.309326171875</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G83" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H83" t="n">
         <v>39</v>
@@ -2805,7 +2805,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G84" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G85" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G86" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G87" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G88" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G89" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G90" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G91" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G92" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G93" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G94" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>686.348205566406</v>
       </c>
       <c r="G95" t="n">
-        <v>610.088195800781</v>
+        <v>610.088134765625</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>657.750366210938</v>
       </c>
       <c r="G100" t="n">
-        <v>584.667846679688</v>
+        <v>584.667724609375</v>
       </c>
       <c r="H100" t="n">
         <v>9</v>
@@ -3298,7 +3298,7 @@
         <v>690.161254882812</v>
       </c>
       <c r="G101" t="n">
-        <v>613.4775390625</v>
+        <v>613.477478027344</v>
       </c>
       <c r="H101" t="n">
         <v>40</v>
@@ -3356,7 +3356,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G103" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H103" t="n">
         <v>4</v>
@@ -3385,7 +3385,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G104" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G105" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G106" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G107" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>662.516662597656</v>
       </c>
       <c r="G108" t="n">
-        <v>588.904541015625</v>
+        <v>588.904479980469</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G109" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H109" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G110" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G114" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G115" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>671.572631835938</v>
       </c>
       <c r="G116" t="n">
-        <v>596.954284667969</v>
+        <v>596.954345703125</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G121" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H121" t="n">
         <v>3</v>
@@ -3907,7 +3907,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G122" t="n">
-        <v>593.141174316406</v>
+        <v>593.141235351562</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G123" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H123" t="n">
         <v>6</v>
@@ -3965,7 +3965,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G124" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G125" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>667.759643554688</v>
       </c>
       <c r="G126" t="n">
-        <v>593.56494140625</v>
+        <v>593.565002441406</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G132" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G133" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G134" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G135" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G136" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G137" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>648.694396972656</v>
       </c>
       <c r="G138" t="n">
-        <v>600.608032226562</v>
+        <v>600.607971191406</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G152" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G153" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G154" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G155" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G156" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G157" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G158" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G159" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G160" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>621.0498046875</v>
       </c>
       <c r="G161" t="n">
-        <v>575.012634277344</v>
+        <v>575.0126953125</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G189" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H189" t="n">
         <v>22</v>
@@ -5879,7 +5879,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G190" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G191" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G192" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G193" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G194" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G195" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G196" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>619.619934082031</v>
       </c>
       <c r="G197" t="n">
-        <v>573.688781738281</v>
+        <v>573.688842773438</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G198" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H198" t="n">
         <v>7</v>
@@ -6140,7 +6140,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G199" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G200" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G201" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G202" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G203" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G204" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G205" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H205" t="n">
         <v>12</v>
@@ -6343,7 +6343,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G206" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H206" t="n">
         <v>1</v>
@@ -6372,7 +6372,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G207" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G208" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G209" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G210" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G211" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G212" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G213" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G214" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>629.152526855469</v>
       </c>
       <c r="G215" t="n">
-        <v>582.514770507812</v>
+        <v>582.514709472656</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G221" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H221" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G222" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G223" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G224" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>609.134033203125</v>
       </c>
       <c r="G225" t="n">
-        <v>563.980163574219</v>
+        <v>563.980224609375</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G226" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H226" t="n">
         <v>4</v>
@@ -6952,7 +6952,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G227" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G228" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G229" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G230" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G231" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>581.489440917969</v>
       </c>
       <c r="G232" t="n">
-        <v>538.384826660156</v>
+        <v>538.384765625</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G233" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H233" t="n">
         <v>7</v>
@@ -7155,7 +7155,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G234" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G235" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G236" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G237" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H237" t="n">
         <v>6</v>
@@ -7271,7 +7271,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G238" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>588.162292480469</v>
       </c>
       <c r="G239" t="n">
-        <v>544.563049316406</v>
+        <v>544.56298828125</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G240" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H240" t="n">
         <v>7</v>
@@ -7358,7 +7358,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G241" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G242" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G243" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G244" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G245" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H245" t="n">
         <v>193</v>
@@ -7503,7 +7503,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G246" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G247" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G248" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G249" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G250" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G251" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G252" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G253" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G254" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G255" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G256" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G257" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>587.209045410156</v>
       </c>
       <c r="G258" t="n">
-        <v>543.680419921875</v>
+        <v>543.680480957031</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G259" t="n">
-        <v>553.389038085938</v>
+        <v>553.388977050781</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -7909,7 +7909,7 @@
         <v>597.694885253906</v>
       </c>
       <c r="G260" t="n">
-        <v>553.389038085938</v>
+        <v>553.388977050781</v>
       </c>
       <c r="H260" t="n">
         <v>6</v>
@@ -8083,7 +8083,7 @@
         <v>627.246032714844</v>
       </c>
       <c r="G266" t="n">
-        <v>580.749572753906</v>
+        <v>580.74951171875</v>
       </c>
       <c r="H266" t="n">
         <v>3</v>
@@ -8431,7 +8431,7 @@
         <v>591.022094726562</v>
       </c>
       <c r="G278" t="n">
-        <v>547.210815429688</v>
+        <v>547.210876464844</v>
       </c>
       <c r="H278" t="n">
         <v>15</v>
@@ -8489,7 +8489,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G280" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H280" t="n">
         <v>9</v>
@@ -8518,7 +8518,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G281" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G282" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>610.087280273438</v>
       </c>
       <c r="G283" t="n">
-        <v>564.86279296875</v>
+        <v>564.862731933594</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G285" t="n">
-        <v>578.101745605469</v>
+        <v>578.101806640625</v>
       </c>
       <c r="H285" t="n">
         <v>29</v>
@@ -8663,7 +8663,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G286" t="n">
-        <v>578.101745605469</v>
+        <v>578.101806640625</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G287" t="n">
-        <v>578.101745605469</v>
+        <v>578.101806640625</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G288" t="n">
-        <v>578.101745605469</v>
+        <v>578.101806640625</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>624.38623046875</v>
       </c>
       <c r="G289" t="n">
-        <v>578.101745605469</v>
+        <v>578.101806640625</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G290" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H290" t="n">
         <v>94</v>
@@ -8808,7 +8808,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G291" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G293" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H293" t="n">
         <v>7</v>
@@ -8895,7 +8895,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G294" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G295" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>638.685119628906</v>
       </c>
       <c r="G296" t="n">
-        <v>591.340698242188</v>
+        <v>591.340759277344</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>645.834594726562</v>
       </c>
       <c r="G298" t="n">
-        <v>597.960144042969</v>
+        <v>597.960205078125</v>
       </c>
       <c r="H298" t="n">
         <v>3</v>
@@ -9127,7 +9127,7 @@
         <v>667.282958984375</v>
       </c>
       <c r="G302" t="n">
-        <v>617.818603515625</v>
+        <v>617.818664550781</v>
       </c>
       <c r="H302" t="n">
         <v>28</v>
@@ -9156,7 +9156,7 @@
         <v>658.70361328125</v>
       </c>
       <c r="G303" t="n">
-        <v>609.875244140625</v>
+        <v>609.875305175781</v>
       </c>
       <c r="H303" t="n">
         <v>3</v>
@@ -9185,7 +9185,7 @@
         <v>655.3671875</v>
       </c>
       <c r="G304" t="n">
-        <v>606.7861328125</v>
+        <v>606.786193847656</v>
       </c>
       <c r="H304" t="n">
         <v>34</v>
@@ -9214,7 +9214,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G305" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H305" t="n">
         <v>6</v>
@@ -9243,7 +9243,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G306" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G307" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G308" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>673.002563476562</v>
       </c>
       <c r="G309" t="n">
-        <v>623.1142578125</v>
+        <v>623.114318847656</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G314" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H314" t="n">
         <v>39</v>
@@ -9504,7 +9504,7 @@
         <v>687.301452636719</v>
       </c>
       <c r="G315" t="n">
-        <v>636.353210449219</v>
+        <v>636.353149414062</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>705.413452148438</v>
       </c>
       <c r="G320" t="n">
-        <v>653.12255859375</v>
+        <v>653.122619628906</v>
       </c>
       <c r="H320" t="n">
         <v>31</v>
@@ -9678,7 +9678,7 @@
         <v>700.647155761719</v>
       </c>
       <c r="G321" t="n">
-        <v>648.709655761719</v>
+        <v>648.709594726562</v>
       </c>
       <c r="H321" t="n">
         <v>9</v>
@@ -9707,7 +9707,7 @@
         <v>714.946044921875</v>
       </c>
       <c r="G322" t="n">
-        <v>661.948608398438</v>
+        <v>661.948547363281</v>
       </c>
       <c r="H322" t="n">
         <v>9</v>
@@ -9736,7 +9736,7 @@
         <v>710.179748535156</v>
       </c>
       <c r="G323" t="n">
-        <v>657.535583496094</v>
+        <v>657.535522460938</v>
       </c>
       <c r="H323" t="n">
         <v>6</v>
@@ -9794,7 +9794,7 @@
         <v>756.889587402344</v>
       </c>
       <c r="G325" t="n">
-        <v>700.783020019531</v>
+        <v>700.782897949219</v>
       </c>
       <c r="H325" t="n">
         <v>4</v>
@@ -9823,7 +9823,7 @@
         <v>770.235229492188</v>
       </c>
       <c r="G326" t="n">
-        <v>713.139221191406</v>
+        <v>713.139282226562</v>
       </c>
       <c r="H326" t="n">
         <v>15</v>
@@ -9881,7 +9881,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G328" t="n">
-        <v>741.38232421875</v>
+        <v>741.382385253906</v>
       </c>
       <c r="H328" t="n">
         <v>34</v>
@@ -9910,7 +9910,7 @@
         <v>800.739562988281</v>
       </c>
       <c r="G329" t="n">
-        <v>741.38232421875</v>
+        <v>741.382385253906</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>781.674377441406</v>
       </c>
       <c r="G330" t="n">
-        <v>723.730529785156</v>
+        <v>723.730407714844</v>
       </c>
       <c r="H330" t="n">
         <v>3</v>
@@ -9997,7 +9997,7 @@
         <v>787.393920898438</v>
       </c>
       <c r="G332" t="n">
-        <v>729.026062011719</v>
+        <v>729.026000976562</v>
       </c>
       <c r="H332" t="n">
         <v>22</v>
@@ -10200,7 +10200,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G339" t="n">
-        <v>732.556457519531</v>
+        <v>732.556396484375</v>
       </c>
       <c r="H339" t="n">
         <v>15</v>
@@ -10229,7 +10229,7 @@
         <v>791.206970214844</v>
       </c>
       <c r="G340" t="n">
-        <v>732.556457519531</v>
+        <v>732.556396484375</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>799.786315917969</v>
       </c>
       <c r="G341" t="n">
-        <v>740.499816894531</v>
+        <v>740.499877929688</v>
       </c>
       <c r="H341" t="n">
         <v>6</v>
@@ -10287,7 +10287,7 @@
         <v>805.505920410156</v>
       </c>
       <c r="G342" t="n">
-        <v>745.795471191406</v>
+        <v>745.79541015625</v>
       </c>
       <c r="H342" t="n">
         <v>25</v>
@@ -10345,7 +10345,7 @@
         <v>822.664611816406</v>
       </c>
       <c r="G344" t="n">
-        <v>761.68212890625</v>
+        <v>761.682189941406</v>
       </c>
       <c r="H344" t="n">
         <v>18</v>
@@ -10403,7 +10403,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G346" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H346" t="n">
         <v>11</v>
@@ -10461,7 +10461,7 @@
         <v>912.747802734375</v>
       </c>
       <c r="G348" t="n">
-        <v>845.087707519531</v>
+        <v>845.087646484375</v>
       </c>
       <c r="H348" t="n">
         <v>69</v>
@@ -10490,7 +10490,7 @@
         <v>969.466857910156</v>
       </c>
       <c r="G349" t="n">
-        <v>897.602294921875</v>
+        <v>897.602233886719</v>
       </c>
       <c r="H349" t="n">
         <v>124</v>
@@ -10548,7 +10548,7 @@
         <v>855.075500488281</v>
       </c>
       <c r="G351" t="n">
-        <v>791.690490722656</v>
+        <v>791.690551757812</v>
       </c>
       <c r="H351" t="n">
         <v>349</v>
@@ -10606,7 +10606,7 @@
         <v>826.477661132812</v>
       </c>
       <c r="G353" t="n">
-        <v>765.212585449219</v>
+        <v>765.212524414062</v>
       </c>
       <c r="H353" t="n">
         <v>69</v>
@@ -10693,7 +10693,7 @@
         <v>848.402648925781</v>
       </c>
       <c r="G356" t="n">
-        <v>785.512329101562</v>
+        <v>785.512268066406</v>
       </c>
       <c r="H356" t="n">
         <v>14</v>
@@ -10780,7 +10780,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G359" t="n">
-        <v>794.338256835938</v>
+        <v>794.338317871094</v>
       </c>
       <c r="H359" t="n">
         <v>1</v>
@@ -10838,7 +10838,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G361" t="n">
-        <v>794.338256835938</v>
+        <v>794.338317871094</v>
       </c>
       <c r="H361" t="n">
         <v>15</v>
@@ -10867,7 +10867,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G362" t="n">
-        <v>794.338256835938</v>
+        <v>794.338317871094</v>
       </c>
       <c r="H362" t="n">
         <v>22</v>
@@ -10925,7 +10925,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G364" t="n">
-        <v>794.338256835938</v>
+        <v>794.338317871094</v>
       </c>
       <c r="H364" t="n">
         <v>114</v>
@@ -10954,7 +10954,7 @@
         <v>857.935241699219</v>
       </c>
       <c r="G365" t="n">
-        <v>794.338256835938</v>
+        <v>794.338317871094</v>
       </c>
       <c r="H365" t="n">
         <v>67</v>
@@ -10983,7 +10983,7 @@
         <v>859.841796875</v>
       </c>
       <c r="G366" t="n">
-        <v>796.103454589844</v>
+        <v>796.103515625</v>
       </c>
       <c r="H366" t="n">
         <v>86</v>
@@ -11128,7 +11128,7 @@
         <v>846.972778320312</v>
       </c>
       <c r="G371" t="n">
-        <v>784.188415527344</v>
+        <v>784.1884765625</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
@@ -11186,7 +11186,7 @@
         <v>847.449401855469</v>
       </c>
       <c r="G373" t="n">
-        <v>784.629638671875</v>
+        <v>784.629699707031</v>
       </c>
       <c r="H373" t="n">
         <v>28</v>
@@ -11215,7 +11215,7 @@
         <v>862.224914550781</v>
       </c>
       <c r="G374" t="n">
-        <v>798.309997558594</v>
+        <v>798.309936523438</v>
       </c>
       <c r="H374" t="n">
         <v>141</v>
@@ -11273,7 +11273,7 @@
         <v>844.589599609375</v>
       </c>
       <c r="G376" t="n">
-        <v>781.981872558594</v>
+        <v>781.98193359375</v>
       </c>
       <c r="H376" t="n">
         <v>121</v>
@@ -11331,7 +11331,7 @@
         <v>840.776550292969</v>
       </c>
       <c r="G378" t="n">
-        <v>778.451477050781</v>
+        <v>778.451538085938</v>
       </c>
       <c r="H378" t="n">
         <v>7</v>
@@ -11360,7 +11360,7 @@
         <v>824.094482421875</v>
       </c>
       <c r="G379" t="n">
-        <v>763.006042480469</v>
+        <v>763.005981445312</v>
       </c>
       <c r="H379" t="n">
         <v>259</v>
@@ -11389,7 +11389,7 @@
         <v>827.907531738281</v>
       </c>
       <c r="G380" t="n">
-        <v>766.536499023438</v>
+        <v>766.536437988281</v>
       </c>
       <c r="H380" t="n">
         <v>36</v>
@@ -11418,7 +11418,7 @@
         <v>829.33740234375</v>
       </c>
       <c r="G381" t="n">
-        <v>767.860290527344</v>
+        <v>767.8603515625</v>
       </c>
       <c r="H381" t="n">
         <v>45</v>
@@ -11534,7 +11534,7 @@
         <v>822.18798828125</v>
       </c>
       <c r="G385" t="n">
-        <v>787.52978515625</v>
+        <v>787.529846191406</v>
       </c>
       <c r="H385" t="n">
         <v>11</v>
@@ -11592,7 +11592,7 @@
         <v>795.973266601562</v>
       </c>
       <c r="G387" t="n">
-        <v>762.420166015625</v>
+        <v>762.420104980469</v>
       </c>
       <c r="H387" t="n">
         <v>140</v>
@@ -11853,7 +11853,7 @@
         <v>827.430908203125</v>
       </c>
       <c r="G396" t="n">
-        <v>792.5517578125</v>
+        <v>792.551818847656</v>
       </c>
       <c r="H396" t="n">
         <v>50</v>
@@ -11940,7 +11940,7 @@
         <v>850.785827636719</v>
       </c>
       <c r="G399" t="n">
-        <v>814.922119140625</v>
+        <v>814.922180175781</v>
       </c>
       <c r="H399" t="n">
         <v>9</v>
@@ -11969,7 +11969,7 @@
         <v>850.785827636719</v>
       </c>
       <c r="G400" t="n">
-        <v>814.922119140625</v>
+        <v>814.922180175781</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G401" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H401" t="n">
         <v>3</v>
@@ -12027,7 +12027,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G402" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G403" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -12085,7 +12085,7 @@
         <v>845.542846679688</v>
       </c>
       <c r="G404" t="n">
-        <v>809.900207519531</v>
+        <v>809.900268554688</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>824.571105957031</v>
       </c>
       <c r="G409" t="n">
-        <v>789.8125</v>
+        <v>789.812438964844</v>
       </c>
       <c r="H409" t="n">
         <v>100</v>
@@ -12288,7 +12288,7 @@
         <v>812.655334472656</v>
       </c>
       <c r="G411" t="n">
-        <v>778.399047851562</v>
+        <v>778.398986816406</v>
       </c>
       <c r="H411" t="n">
         <v>72</v>
@@ -12607,7 +12607,7 @@
         <v>894.1591796875</v>
       </c>
       <c r="G422" t="n">
-        <v>856.467163085938</v>
+        <v>856.467224121094</v>
       </c>
       <c r="H422" t="n">
         <v>33</v>
@@ -12694,7 +12694,7 @@
         <v>904.645080566406</v>
       </c>
       <c r="G425" t="n">
-        <v>866.511108398438</v>
+        <v>866.511047363281</v>
       </c>
       <c r="H425" t="n">
         <v>1</v>
@@ -12781,7 +12781,7 @@
         <v>895.589111328125</v>
       </c>
       <c r="G428" t="n">
-        <v>857.836853027344</v>
+        <v>857.836791992188</v>
       </c>
       <c r="H428" t="n">
         <v>78</v>
@@ -12955,7 +12955,7 @@
         <v>942.298889160156</v>
       </c>
       <c r="G434" t="n">
-        <v>902.577697753906</v>
+        <v>902.57763671875</v>
       </c>
       <c r="H434" t="n">
         <v>56</v>
@@ -13216,7 +13216,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G443" t="n">
-        <v>1010.77746582031</v>
+        <v>1010.77734375</v>
       </c>
       <c r="H443" t="n">
         <v>187</v>
@@ -13245,7 +13245,7 @@
         <v>1055.26037597656</v>
       </c>
       <c r="G444" t="n">
-        <v>1010.77746582031</v>
+        <v>1010.77734375</v>
       </c>
       <c r="H444" t="n">
         <v>22</v>
@@ -13274,7 +13274,7 @@
         <v>1105.783203125</v>
       </c>
       <c r="G445" t="n">
-        <v>1059.17041015625</v>
+        <v>1059.17053222656</v>
       </c>
       <c r="H445" t="n">
         <v>103</v>
@@ -13390,7 +13390,7 @@
         <v>1057.16687011719</v>
       </c>
       <c r="G449" t="n">
-        <v>1012.60345458984</v>
+        <v>1012.60357666016</v>
       </c>
       <c r="H449" t="n">
         <v>39</v>
@@ -13419,7 +13419,7 @@
         <v>1047.63427734375</v>
       </c>
       <c r="G450" t="n">
-        <v>1003.47277832031</v>
+        <v>1003.47271728516</v>
       </c>
       <c r="H450" t="n">
         <v>20</v>
@@ -13448,7 +13448,7 @@
         <v>1035.24194335938</v>
       </c>
       <c r="G451" t="n">
-        <v>991.602844238281</v>
+        <v>991.602783203125</v>
       </c>
       <c r="H451" t="n">
         <v>12</v>
@@ -13477,7 +13477,7 @@
         <v>1013.31689453125</v>
       </c>
       <c r="G452" t="n">
-        <v>970.601989746094</v>
+        <v>970.601928710938</v>
       </c>
       <c r="H452" t="n">
         <v>3</v>
@@ -13564,7 +13564,7 @@
         <v>1043.8212890625</v>
       </c>
       <c r="G455" t="n">
-        <v>999.820495605469</v>
+        <v>999.820556640625</v>
       </c>
       <c r="H455" t="n">
         <v>188</v>
@@ -13651,7 +13651,7 @@
         <v>1061.93322753906</v>
       </c>
       <c r="G458" t="n">
-        <v>1017.16888427734</v>
+        <v>1017.16900634766</v>
       </c>
       <c r="H458" t="n">
         <v>240</v>
@@ -13825,7 +13825,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G464" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H464" t="n">
         <v>61</v>
@@ -14144,7 +14144,7 @@
         <v>1074.32556152344</v>
       </c>
       <c r="G475" t="n">
-        <v>1029.03894042969</v>
+        <v>1029.0390625</v>
       </c>
       <c r="H475" t="n">
         <v>40</v>
@@ -14202,7 +14202,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G477" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H477" t="n">
         <v>22</v>
@@ -14376,7 +14376,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G483" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H483" t="n">
         <v>45</v>
@@ -14492,7 +14492,7 @@
         <v>950.878234863281</v>
       </c>
       <c r="G487" t="n">
-        <v>910.795349121094</v>
+        <v>910.795288085938</v>
       </c>
       <c r="H487" t="n">
         <v>12</v>
@@ -14521,7 +14521,7 @@
         <v>958.98095703125</v>
       </c>
       <c r="G488" t="n">
-        <v>918.556457519531</v>
+        <v>918.556518554688</v>
       </c>
       <c r="H488" t="n">
         <v>1</v>
@@ -14550,7 +14550,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G489" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H489" t="n">
         <v>1</v>
@@ -14608,7 +14608,7 @@
         <v>988.532104492188</v>
       </c>
       <c r="G491" t="n">
-        <v>946.861938476562</v>
+        <v>946.861877441406</v>
       </c>
       <c r="H491" t="n">
         <v>20</v>
@@ -14637,7 +14637,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G492" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H492" t="n">
         <v>36</v>
@@ -14666,7 +14666,7 @@
         <v>985.672302246094</v>
       </c>
       <c r="G493" t="n">
-        <v>944.122741699219</v>
+        <v>944.122680664062</v>
       </c>
       <c r="H493" t="n">
         <v>1</v>
@@ -14695,7 +14695,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G494" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H494" t="n">
         <v>6</v>
@@ -14724,7 +14724,7 @@
         <v>963.747253417969</v>
       </c>
       <c r="G495" t="n">
-        <v>923.121887207031</v>
+        <v>923.121826171875</v>
       </c>
       <c r="H495" t="n">
         <v>18</v>
@@ -14753,7 +14753,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G496" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H496" t="n">
         <v>129</v>
@@ -14782,7 +14782,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G497" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H497" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G499" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H499" t="n">
         <v>22</v>
@@ -14898,7 +14898,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G501" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H501" t="n">
         <v>55</v>
@@ -14927,7 +14927,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G502" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G503" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H503" t="n">
         <v>6</v>
@@ -14985,7 +14985,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G504" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G505" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G506" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H506" t="n">
         <v>147</v>
@@ -15072,7 +15072,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G507" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G508" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G509" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G510" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G511" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H511" t="n">
         <v>33</v>
@@ -15217,7 +15217,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G512" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H512" t="n">
         <v>9</v>
@@ -15246,7 +15246,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G513" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15275,7 +15275,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G514" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G515" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G516" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G517" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H517" t="n">
         <v>3</v>
@@ -15449,7 +15449,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G520" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H520" t="n">
         <v>3</v>
@@ -15623,7 +15623,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G526" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H526" t="n">
         <v>48</v>
@@ -15652,7 +15652,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G527" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H527" t="n">
         <v>51</v>
@@ -15681,7 +15681,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G528" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H528" t="n">
         <v>202</v>
@@ -15710,7 +15710,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G529" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H529" t="n">
         <v>3</v>
@@ -15739,7 +15739,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G530" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H530" t="n">
         <v>18</v>
@@ -15826,7 +15826,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G533" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H533" t="n">
         <v>11</v>
@@ -15855,7 +15855,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G534" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H534" t="n">
         <v>20</v>
@@ -15884,7 +15884,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G535" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H535" t="n">
         <v>0</v>
@@ -15913,7 +15913,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G536" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H536" t="n">
         <v>28</v>
@@ -15942,7 +15942,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G537" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H537" t="n">
         <v>31</v>
@@ -15971,7 +15971,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G538" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H538" t="n">
         <v>62</v>
@@ -16029,7 +16029,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G540" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H540" t="n">
         <v>4</v>
@@ -16116,7 +16116,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G543" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H543" t="n">
         <v>1</v>
@@ -16348,7 +16348,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G551" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H551" t="n">
         <v>6</v>
@@ -16406,7 +16406,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G553" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H553" t="n">
         <v>1</v>
@@ -16464,7 +16464,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G555" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H555" t="n">
         <v>214</v>
@@ -16493,7 +16493,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G556" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H556" t="n">
         <v>15</v>
@@ -16522,7 +16522,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G557" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H557" t="n">
         <v>15</v>
@@ -16551,7 +16551,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G558" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H558" t="n">
         <v>72</v>
@@ -16580,7 +16580,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G559" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H559" t="n">
         <v>103</v>
@@ -16609,7 +16609,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G560" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H560" t="n">
         <v>39</v>
@@ -16783,7 +16783,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G566" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H566" t="n">
         <v>51</v>
@@ -16812,7 +16812,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G567" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G568" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H568" t="n">
         <v>4</v>
@@ -16870,7 +16870,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G569" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H569" t="n">
         <v>3</v>
@@ -16899,7 +16899,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G570" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H570" t="n">
         <v>3</v>
@@ -16928,7 +16928,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G571" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G572" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H572" t="n">
         <v>14</v>
@@ -16986,7 +16986,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G573" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H573" t="n">
         <v>7</v>
@@ -17015,7 +17015,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G574" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H574" t="n">
         <v>34</v>
@@ -17102,7 +17102,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G577" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H577" t="n">
         <v>89</v>
@@ -17131,7 +17131,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G578" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G579" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H579" t="n">
         <v>1</v>
@@ -17189,7 +17189,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G580" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G581" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H581" t="n">
         <v>6</v>
@@ -17247,7 +17247,7 @@
         <v>977.092956542969</v>
       </c>
       <c r="G582" t="n">
-        <v>935.904968261719</v>
+        <v>935.905029296875</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>1005.69079589844</v>
       </c>
       <c r="G585" t="n">
-        <v>963.297302246094</v>
+        <v>963.29736328125</v>
       </c>
       <c r="H585" t="n">
         <v>4</v>
@@ -17363,7 +17363,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G586" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H586" t="n">
         <v>18</v>
@@ -17392,7 +17392,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G587" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G588" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H588" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G589" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G590" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G591" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -17537,7 +17537,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G592" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G593" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G594" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G595" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G596" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H596" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G597" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H597" t="n">
         <v>0</v>
@@ -17711,7 +17711,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G598" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H598" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G600" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H600" t="n">
         <v>1</v>
@@ -17798,7 +17798,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G601" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H601" t="n">
         <v>1</v>
@@ -17827,7 +17827,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G602" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H602" t="n">
         <v>9</v>
@@ -17856,7 +17856,7 @@
         <v>981.859252929688</v>
       </c>
       <c r="G603" t="n">
-        <v>940.470397949219</v>
+        <v>940.470336914062</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -17914,7 +17914,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G605" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H605" t="n">
         <v>50</v>
@@ -17943,7 +17943,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G606" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H606" t="n">
         <v>23</v>
@@ -17972,7 +17972,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G607" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H607" t="n">
         <v>12</v>
@@ -18001,7 +18001,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G608" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H608" t="n">
         <v>15</v>
@@ -18030,7 +18030,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G609" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H609" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>1029.52233886719</v>
       </c>
       <c r="G610" t="n">
-        <v>986.124267578125</v>
+        <v>986.124328613281</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18117,7 +18117,7 @@
         <v>1010.45709228516</v>
       </c>
       <c r="G612" t="n">
-        <v>967.862731933594</v>
+        <v>967.862670898438</v>
       </c>
       <c r="H612" t="n">
         <v>25</v>
@@ -18146,7 +18146,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G613" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H613" t="n">
         <v>3</v>
@@ -18262,7 +18262,7 @@
         <v>991.391845703125</v>
       </c>
       <c r="G617" t="n">
-        <v>949.601135253906</v>
+        <v>949.601196289062</v>
       </c>
       <c r="H617" t="n">
         <v>3</v>
@@ -18291,7 +18291,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G618" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H618" t="n">
         <v>240</v>
@@ -18378,7 +18378,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G621" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H621" t="n">
         <v>7</v>
@@ -18407,7 +18407,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G622" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G623" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H623" t="n">
         <v>3</v>
@@ -18465,7 +18465,7 @@
         <v>958.027709960938</v>
       </c>
       <c r="G624" t="n">
-        <v>917.643432617188</v>
+        <v>917.643371582031</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>962.794006347656</v>
       </c>
       <c r="G625" t="n">
-        <v>922.208801269531</v>
+        <v>922.208862304688</v>
       </c>
       <c r="H625" t="n">
         <v>4</v>
@@ -18523,7 +18523,7 @@
         <v>953.261413574219</v>
       </c>
       <c r="G626" t="n">
-        <v>913.078063964844</v>
+        <v>913.078002929688</v>
       </c>
       <c r="H626" t="n">
         <v>18</v>
@@ -80154,6 +80154,35 @@
         <v>0</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
